--- a/database/event/5147/event_5147_evp_summary.xlsx
+++ b/database/event/5147/event_5147_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.7734</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0777</v>
+        <v>3.0068</v>
       </c>
       <c r="E2" t="n">
         <v>8.6615</v>
@@ -548,7 +548,7 @@
         <v>1.4776</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4941</v>
+        <v>2.4313</v>
       </c>
       <c r="E3" t="n">
         <v>7.2168</v>
@@ -594,7 +594,7 @@
         <v>1.4114</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3634</v>
+        <v>2.3024</v>
       </c>
       <c r="E4" t="n">
         <v>6.8933</v>
@@ -640,7 +640,7 @@
         <v>1.0497</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6497</v>
+        <v>1.5985</v>
       </c>
       <c r="E5" t="n">
         <v>5.1266</v>
@@ -686,7 +686,7 @@
         <v>0.8265</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2094</v>
+        <v>1.1643</v>
       </c>
       <c r="E6" t="n">
         <v>4.0367</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9141</v>
+        <v>3.9064</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8014</v>
+        <v>0.7998</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1598</v>
+        <v>1.1124</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9141</v>
+        <v>3.9064</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0734</v>
+        <v>2.0657</v>
       </c>
       <c r="G7" t="n">
         <v>1.8407</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0734</v>
+        <v>2.0657</v>
       </c>
       <c r="I7" t="n">
         <v>2.0831</v>
@@ -778,7 +778,7 @@
         <v>0.7751</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1081</v>
+        <v>1.0644</v>
       </c>
       <c r="E8" t="n">
         <v>3.7859</v>
@@ -824,7 +824,7 @@
         <v>0.5913</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7454</v>
+        <v>0.7067</v>
       </c>
       <c r="E9" t="n">
         <v>2.8881</v>
@@ -870,7 +870,7 @@
         <v>0.5502</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6643</v>
+        <v>0.6268</v>
       </c>
       <c r="E10" t="n">
         <v>2.6874</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.21</v>
+        <v>2.2004</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4525</v>
+        <v>0.4505</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4714</v>
+        <v>0.4327</v>
       </c>
       <c r="E11" t="n">
-        <v>2.21</v>
+        <v>2.2004</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5848</v>
+        <v>2.5752</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3748</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5848</v>
+        <v>2.5752</v>
       </c>
       <c r="I11" t="n">
         <v>2.5969</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2016</v>
+        <v>2.1971</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4508</v>
+        <v>0.4498</v>
       </c>
       <c r="D12" t="n">
-        <v>0.468</v>
+        <v>0.4314</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2016</v>
+        <v>2.1971</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2228</v>
+        <v>1.2183</v>
       </c>
       <c r="G12" t="n">
         <v>0.9788</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2228</v>
+        <v>1.2183</v>
       </c>
       <c r="I12" t="n">
         <v>1.2285</v>
@@ -1008,7 +1008,7 @@
         <v>0.4426</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4519</v>
+        <v>0.4173</v>
       </c>
       <c r="E13" t="n">
         <v>2.1616</v>
@@ -1054,7 +1054,7 @@
         <v>0.4125</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3925</v>
+        <v>0.3587</v>
       </c>
       <c r="E14" t="n">
         <v>2.0147</v>
@@ -1100,7 +1100,7 @@
         <v>0.4002</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3683</v>
+        <v>0.3348</v>
       </c>
       <c r="E15" t="n">
         <v>1.9546</v>
@@ -1146,7 +1146,7 @@
         <v>0.3371</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2438</v>
+        <v>0.2121</v>
       </c>
       <c r="E16" t="n">
         <v>1.6466</v>
@@ -1192,7 +1192,7 @@
         <v>0.2826</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1362</v>
+        <v>0.1059</v>
       </c>
       <c r="E17" t="n">
         <v>1.3801</v>
@@ -1238,7 +1238,7 @@
         <v>0.2218</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0162</v>
+        <v>-0.0124</v>
       </c>
       <c r="E18" t="n">
         <v>1.0831</v>
@@ -1284,7 +1284,7 @@
         <v>0.1823</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0617</v>
+        <v>-0.0893</v>
       </c>
       <c r="E19" t="n">
         <v>0.8902</v>
@@ -1330,7 +1330,7 @@
         <v>0.1712</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0835</v>
+        <v>-0.1107</v>
       </c>
       <c r="E20" t="n">
         <v>0.8363</v>
@@ -1376,7 +1376,7 @@
         <v>0.1705</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.1122</v>
       </c>
       <c r="E21" t="n">
         <v>0.8326</v>
@@ -1422,7 +1422,7 @@
         <v>0.081</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2615</v>
+        <v>-0.2863</v>
       </c>
       <c r="E22" t="n">
         <v>0.3956</v>
@@ -1468,7 +1468,7 @@
         <v>0.079</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2656</v>
+        <v>-0.2903</v>
       </c>
       <c r="E23" t="n">
         <v>0.3856</v>
@@ -1514,7 +1514,7 @@
         <v>0.0526</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3176</v>
+        <v>-0.3416</v>
       </c>
       <c r="E24" t="n">
         <v>0.2569</v>
@@ -1560,7 +1560,7 @@
         <v>0.0105</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4006</v>
+        <v>-0.4234</v>
       </c>
       <c r="E25" t="n">
         <v>0.0515</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0102</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4416</v>
+        <v>-0.4638</v>
       </c>
       <c r="E26" t="n">
         <v>-0.05</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0682</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5558</v>
+        <v>-0.5765</v>
       </c>
       <c r="E27" t="n">
         <v>-0.3329</v>
@@ -1698,7 +1698,7 @@
         <v>-0.07439999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5682</v>
+        <v>-0.5887</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3634</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1714</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7595</v>
+        <v>-0.7774</v>
       </c>
       <c r="E29" t="n">
         <v>-0.8371</v>
@@ -1790,7 +1790,7 @@
         <v>-0.195</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8061</v>
+        <v>-0.8233</v>
       </c>
       <c r="E30" t="n">
         <v>-0.9524</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2302</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.8918</v>
       </c>
       <c r="E31" t="n">
         <v>-1.1241</v>
@@ -1882,7 +1882,7 @@
         <v>-0.2576</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9295</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="E32" t="n">
         <v>-1.2579</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.2896</v>
+        <v>-1.2903</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.264</v>
+        <v>-0.2642</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9423</v>
+        <v>-0.958</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2896</v>
+        <v>-1.2903</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1935</v>
+        <v>0.1928</v>
       </c>
       <c r="G33" t="n">
         <v>-1.4831</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1935</v>
+        <v>0.1928</v>
       </c>
       <c r="I33" t="n">
         <v>0.1944</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2954</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0042</v>
+        <v>-1.0187</v>
       </c>
       <c r="E34" t="n">
         <v>-1.4427</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3306</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0736</v>
+        <v>-1.0872</v>
       </c>
       <c r="E35" t="n">
         <v>-1.6146</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6785</v>
+        <v>-1.6788</v>
       </c>
       <c r="C36" t="n">
         <v>-0.3437</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0994</v>
+        <v>-1.1127</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6785</v>
+        <v>-1.6788</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0675</v>
+        <v>0.0672</v>
       </c>
       <c r="G36" t="n">
         <v>-1.746</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0675</v>
+        <v>0.0672</v>
       </c>
       <c r="I36" t="n">
         <v>0.0678</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3526</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1171</v>
+        <v>-1.1301</v>
       </c>
       <c r="E37" t="n">
         <v>-1.7223</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3678</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.147</v>
+        <v>-1.1596</v>
       </c>
       <c r="E38" t="n">
         <v>-1.7963</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4639</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3367</v>
+        <v>-1.3466</v>
       </c>
       <c r="E39" t="n">
         <v>-2.2659</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6597</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.723</v>
+        <v>-1.7276</v>
       </c>
       <c r="E40" t="n">
         <v>-3.2221</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6634</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7303</v>
+        <v>-1.7348</v>
       </c>
       <c r="E41" t="n">
         <v>-3.2401</v>

--- a/database/event/5147/event_5147_evp_summary.xlsx
+++ b/database/event/5147/event_5147_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.6615</v>
+        <v>7.904</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7734</v>
+        <v>1.6183</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0068</v>
+        <v>2.9302</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6615</v>
+        <v>7.904</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1781</v>
+        <v>3.6078</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4834</v>
+        <v>4.2962</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2488</v>
+        <v>7.2254</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4438</v>
+        <v>3.7569</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4834</v>
+        <v>4.2962</v>
       </c>
       <c r="K2" t="n">
         <v>126</v>
@@ -529,7 +529,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>7.927199999999999</v>
+        <v>8.053100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.2168</v>
+        <v>6.7598</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4776</v>
+        <v>1.384</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4313</v>
+        <v>2.4137</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2168</v>
+        <v>6.7598</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8295</v>
+        <v>2.9444</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3872</v>
+        <v>3.8154</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8295</v>
+        <v>4.8879</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2934</v>
+        <v>2.5415</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3872</v>
+        <v>3.8154</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>6.6806</v>
+        <v>6.3569</v>
       </c>
       <c r="N3" t="n">
         <v>299</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8933</v>
+        <v>6.1995</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4114</v>
+        <v>1.2693</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3024</v>
+        <v>2.1608</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8933</v>
+        <v>6.1995</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5705</v>
+        <v>3.182</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3228</v>
+        <v>3.0175</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5705</v>
+        <v>5.7249</v>
       </c>
       <c r="I4" t="n">
-        <v>2.894</v>
+        <v>2.9767</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3228</v>
+        <v>3.0175</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -621,7 +621,7 @@
         <v>183</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2168</v>
+        <v>5.9942</v>
       </c>
       <c r="N4" t="n">
         <v>299</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1266</v>
+        <v>5.1733</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0497</v>
+        <v>1.0592</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5985</v>
+        <v>1.6975</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1266</v>
+        <v>5.1733</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0943</v>
+        <v>2.6036</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0323</v>
+        <v>2.5697</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0943</v>
+        <v>3.6871</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6975</v>
+        <v>1.9171</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0323</v>
+        <v>2.5697</v>
       </c>
       <c r="K5" t="n">
         <v>126</v>
@@ -667,7 +667,7 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7298</v>
+        <v>4.486800000000001</v>
       </c>
       <c r="N5" t="n">
         <v>284</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0367</v>
+        <v>4.1459</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8265</v>
+        <v>0.8489</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1643</v>
+        <v>1.2337</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0367</v>
+        <v>4.1459</v>
       </c>
       <c r="F6" t="n">
-        <v>2.522</v>
+        <v>2.7397</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5147</v>
+        <v>1.4062</v>
       </c>
       <c r="H6" t="n">
-        <v>2.522</v>
+        <v>4.1667</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0442</v>
+        <v>2.1665</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5147</v>
+        <v>1.4062</v>
       </c>
       <c r="K6" t="n">
         <v>116</v>
@@ -713,7 +713,7 @@
         <v>183</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5589</v>
+        <v>3.5727</v>
       </c>
       <c r="N6" t="n">
         <v>299</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9064</v>
+        <v>3.7192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7998</v>
+        <v>0.7615</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1124</v>
+        <v>1.041</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9064</v>
+        <v>3.7192</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0657</v>
+        <v>3.0806</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8407</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0657</v>
+        <v>5.3678</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0831</v>
+        <v>2.791</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8407</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L7" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9238</v>
+        <v>3.4296</v>
       </c>
       <c r="N7" t="n">
-        <v>229</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7859</v>
+        <v>3.5416</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7751</v>
+        <v>0.7251</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0644</v>
+        <v>0.9608</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7859</v>
+        <v>3.5416</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3235</v>
+        <v>2.0761</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4624</v>
+        <v>1.4655</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3235</v>
+        <v>2.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6938</v>
+        <v>2.1615</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4624</v>
+        <v>1.4655</v>
       </c>
       <c r="K8" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L8" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1562</v>
+        <v>3.627</v>
       </c>
       <c r="N8" t="n">
-        <v>284</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8881</v>
+        <v>3.324</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5913</v>
+        <v>0.6806</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7067</v>
+        <v>0.8626</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8881</v>
+        <v>3.324</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2255</v>
+        <v>2.5231</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6626</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2255</v>
+        <v>3.4036</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2255</v>
+        <v>1.7697</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6626</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8881</v>
+        <v>2.5706</v>
       </c>
       <c r="N9" t="n">
-        <v>246</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6874</v>
+        <v>2.7418</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5502</v>
+        <v>0.5614</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6268</v>
+        <v>0.5998</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6874</v>
+        <v>2.7418</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0588</v>
+        <v>2.0134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6286</v>
+        <v>0.7284</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0588</v>
+        <v>2.0134</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6687</v>
+        <v>2.0962</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6286</v>
+        <v>0.7284</v>
       </c>
       <c r="K10" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L10" t="n">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2973</v>
+        <v>2.8246</v>
       </c>
       <c r="N10" t="n">
-        <v>299</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2004</v>
+        <v>2.6903</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4505</v>
+        <v>0.5508</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4327</v>
+        <v>0.5765</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2004</v>
+        <v>2.6903</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5752</v>
+        <v>2.8453</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3748</v>
+        <v>-0.155</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5752</v>
+        <v>2.8881</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5969</v>
+        <v>3.0069</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3748</v>
+        <v>-0.155</v>
       </c>
       <c r="K11" t="n">
         <v>123</v>
@@ -943,7 +943,7 @@
         <v>106</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2221</v>
+        <v>2.8519</v>
       </c>
       <c r="N11" t="n">
         <v>229</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1971</v>
+        <v>2.5333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4498</v>
+        <v>0.5187</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4314</v>
+        <v>0.5056</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1971</v>
+        <v>2.5333</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2183</v>
+        <v>1.3397</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9788</v>
+        <v>1.1936</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2183</v>
+        <v>1.3397</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2285</v>
+        <v>1.3397</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9788</v>
+        <v>1.1936</v>
       </c>
       <c r="K12" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="L12" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2073</v>
+        <v>2.5333</v>
       </c>
       <c r="N12" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1616</v>
+        <v>2.3581</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4426</v>
+        <v>0.4828</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4173</v>
+        <v>0.4266</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1616</v>
+        <v>2.3581</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2909</v>
+        <v>1.5583</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8707</v>
+        <v>0.7998</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2909</v>
+        <v>1.5583</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2909</v>
+        <v>1.5583</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8707</v>
+        <v>0.7998</v>
       </c>
       <c r="K13" t="n">
         <v>109</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1616</v>
+        <v>2.3581</v>
       </c>
       <c r="N13" t="n">
         <v>163</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0147</v>
+        <v>2.3162</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4125</v>
+        <v>0.4742</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3587</v>
+        <v>0.4076</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0147</v>
+        <v>2.3162</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1119</v>
+        <v>2.2929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9028</v>
+        <v>0.0233</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1119</v>
+        <v>2.5923</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1119</v>
+        <v>1.3479</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9028</v>
+        <v>0.0233</v>
       </c>
       <c r="K14" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L14" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0147</v>
+        <v>1.3712</v>
       </c>
       <c r="N14" t="n">
-        <v>246</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9546</v>
+        <v>1.9993</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4002</v>
+        <v>0.4093</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3348</v>
+        <v>0.2646</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9546</v>
+        <v>1.9993</v>
       </c>
       <c r="F15" t="n">
-        <v>1.16</v>
+        <v>1.1847</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7946</v>
+        <v>0.8146</v>
       </c>
       <c r="H15" t="n">
-        <v>1.16</v>
+        <v>1.1847</v>
       </c>
       <c r="I15" t="n">
-        <v>1.16</v>
+        <v>1.1847</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7946</v>
+        <v>0.8146</v>
       </c>
       <c r="K15" t="n">
         <v>109</v>
@@ -1127,7 +1127,7 @@
         <v>54</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9546</v>
+        <v>1.9993</v>
       </c>
       <c r="N15" t="n">
         <v>163</v>
@@ -1136,81 +1136,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6466</v>
+        <v>1.9327</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3371</v>
+        <v>0.3957</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2121</v>
+        <v>0.2345</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6466</v>
+        <v>1.9327</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7722</v>
+        <v>1.3214</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8744</v>
+        <v>0.6113</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7722</v>
+        <v>1.3214</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7722</v>
+        <v>1.3214</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8744</v>
+        <v>0.6113</v>
       </c>
       <c r="K16" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="L16" t="n">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6466</v>
+        <v>1.9327</v>
       </c>
       <c r="N16" t="n">
-        <v>161</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3801</v>
+        <v>1.856</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2826</v>
+        <v>0.38</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1059</v>
+        <v>0.1999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3801</v>
+        <v>1.856</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4233</v>
+        <v>0.9867</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0432</v>
+        <v>0.8693</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4233</v>
+        <v>0.9867</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4233</v>
+        <v>0.9867</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0432</v>
+        <v>0.8693</v>
       </c>
       <c r="K17" t="n">
         <v>105</v>
@@ -1219,7 +1219,7 @@
         <v>56</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3801</v>
+        <v>1.856</v>
       </c>
       <c r="N17" t="n">
         <v>161</v>
@@ -1228,553 +1228,553 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0831</v>
+        <v>1.3755</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2218</v>
+        <v>0.2816</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0124</v>
+        <v>-0.017</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0831</v>
+        <v>1.3755</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2217</v>
+        <v>1.3007</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3048</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2217</v>
+        <v>1.3007</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2217</v>
+        <v>1.3007</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3048</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="L18" t="n">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0831</v>
+        <v>1.3755</v>
       </c>
       <c r="N18" t="n">
-        <v>246</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8902</v>
+        <v>1.2168</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1823</v>
+        <v>0.2491</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0893</v>
+        <v>-0.0887</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8902</v>
+        <v>1.2168</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8902</v>
+        <v>1.572</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.3552</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8902</v>
+        <v>1.572</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8902</v>
+        <v>1.572</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.3552</v>
       </c>
       <c r="K19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8902</v>
+        <v>1.2168</v>
       </c>
       <c r="N19" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8363</v>
+        <v>1.1103</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1712</v>
+        <v>0.2273</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1107</v>
+        <v>-0.1368</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8363</v>
+        <v>1.1103</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4048</v>
+        <v>1.1103</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5685</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4048</v>
+        <v>1.1103</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4048</v>
+        <v>1.1103</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5685</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8363</v>
+        <v>1.1103</v>
       </c>
       <c r="N20" t="n">
-        <v>163</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8326</v>
+        <v>1.0747</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1705</v>
+        <v>0.22</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1122</v>
+        <v>-0.1528</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8326</v>
+        <v>1.0747</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2312</v>
+        <v>0.015</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3986</v>
+        <v>1.0597</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2312</v>
+        <v>0.015</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9979</v>
+        <v>0.015</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3986</v>
+        <v>1.0597</v>
       </c>
       <c r="K21" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="L21" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5992999999999999</v>
+        <v>1.0747</v>
       </c>
       <c r="N21" t="n">
-        <v>284</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3956</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.081</v>
+        <v>0.1483</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2863</v>
+        <v>-0.311</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3956</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0182</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4138</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0182</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0182</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4138</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L22" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3956</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>161</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3856</v>
+        <v>0.619</v>
       </c>
       <c r="C23" t="n">
-        <v>0.079</v>
+        <v>0.1267</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2903</v>
+        <v>-0.3586</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3856</v>
+        <v>0.619</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3856</v>
+        <v>0.619</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3856</v>
+        <v>0.619</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3856</v>
+        <v>0.619</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3856</v>
+        <v>0.619</v>
       </c>
       <c r="N23" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2569</v>
+        <v>0.6131</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0526</v>
+        <v>0.1255</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3416</v>
+        <v>-0.3612</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2569</v>
+        <v>0.6131</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2569</v>
+        <v>1.2971</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2569</v>
+        <v>1.2971</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2569</v>
+        <v>1.2971</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2569</v>
+        <v>0.6130999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>102</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0515</v>
+        <v>0.5161</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0105</v>
+        <v>0.1057</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4234</v>
+        <v>-0.405</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0515</v>
+        <v>0.5161</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0515</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.4296</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0515</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0515</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.4296</v>
       </c>
       <c r="K25" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0515</v>
+        <v>0.5161</v>
       </c>
       <c r="N25" t="n">
-        <v>106</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.05</v>
+        <v>0.4957</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0102</v>
+        <v>0.1015</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4638</v>
+        <v>-0.4142</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.05</v>
+        <v>0.4957</v>
       </c>
       <c r="F26" t="n">
-        <v>0.95</v>
+        <v>0.4957</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.95</v>
+        <v>0.4957</v>
       </c>
       <c r="I26" t="n">
-        <v>0.95</v>
+        <v>0.4957</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.05000000000000004</v>
+        <v>0.4957</v>
       </c>
       <c r="N26" t="n">
-        <v>161</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3329</v>
+        <v>0.0261</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0682</v>
+        <v>0.0053</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5765</v>
+        <v>-0.6262</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3329</v>
+        <v>0.0261</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0538</v>
+        <v>1.6415</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7209</v>
+        <v>-1.6154</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.0538</v>
+        <v>1.6415</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8541</v>
+        <v>1.6415</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7209</v>
+        <v>-1.6154</v>
       </c>
       <c r="K27" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L27" t="n">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1332</v>
+        <v>0.02610000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>299</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3634</v>
+        <v>-0.1827</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0374</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5887</v>
+        <v>-0.7205</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3634</v>
+        <v>-0.1827</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5428</v>
+        <v>-1.1268</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.9062</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5428</v>
+        <v>-1.1268</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5428</v>
+        <v>-0.5859</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.9062</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L28" t="n">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3633999999999999</v>
+        <v>0.3582000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>246</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>kRYSTAL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.8371</v>
+        <v>-0.4504</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1714</v>
+        <v>-0.0922</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7774</v>
+        <v>-0.8413</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.8371</v>
+        <v>-0.4504</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.8371</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-1.0235</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.8371</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8371</v>
+        <v>0.5967</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-1.0235</v>
       </c>
       <c r="K29" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.8371</v>
+        <v>-0.4268000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>102</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.9524</v>
+        <v>-0.5712</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.195</v>
+        <v>-0.117</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8233</v>
+        <v>-0.8959</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.9524</v>
+        <v>-0.5712</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.9524</v>
+        <v>-0.5712</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.9524</v>
+        <v>-0.5712</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.9524</v>
+        <v>-0.5712</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.9524</v>
+        <v>-0.5712</v>
       </c>
       <c r="N30" t="n">
         <v>102</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.1241</v>
+        <v>-0.604</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2302</v>
+        <v>-0.1237</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8918</v>
+        <v>-0.9107</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.1241</v>
+        <v>-0.604</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.1241</v>
+        <v>-0.604</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.1241</v>
+        <v>-0.604</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.1241</v>
+        <v>-0.604</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.1241</v>
+        <v>-0.604</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.2579</v>
+        <v>-0.8227</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2576</v>
+        <v>-0.1684</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-1.0094</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.2579</v>
+        <v>-0.8227</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7948</v>
+        <v>-0.8227</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4631</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7948</v>
+        <v>-0.8227</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7948</v>
+        <v>-0.8227</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4631</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L32" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.2579</v>
+        <v>-0.8227</v>
       </c>
       <c r="N32" t="n">
-        <v>161</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kRYSTAL</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.2903</v>
+        <v>-0.8547</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2642</v>
+        <v>-0.175</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.958</v>
+        <v>-1.0239</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2903</v>
+        <v>-0.8547</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1928</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.4831</v>
+        <v>-0.2907</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1928</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1944</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.4831</v>
+        <v>-0.2907</v>
       </c>
       <c r="K33" t="n">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="L33" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.2887</v>
+        <v>-0.8547</v>
       </c>
       <c r="N33" t="n">
-        <v>229</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.4427</v>
+        <v>-0.9115</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2954</v>
+        <v>-0.1866</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0187</v>
+        <v>-1.0495</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.4427</v>
+        <v>-0.9115</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.4427</v>
+        <v>-0.9115</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.4427</v>
+        <v>-0.9115</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.4427</v>
+        <v>-0.9115</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.4427</v>
+        <v>-0.9115</v>
       </c>
       <c r="N34" t="n">
         <v>106</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.6146</v>
+        <v>-1.024</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3306</v>
+        <v>-0.2097</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0872</v>
+        <v>-1.1003</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.6146</v>
+        <v>-1.024</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.6146</v>
+        <v>-1.024</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.6146</v>
+        <v>-1.024</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.6146</v>
+        <v>-1.024</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.6146</v>
+        <v>-1.024</v>
       </c>
       <c r="N35" t="n">
         <v>102</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6788</v>
+        <v>-1.1633</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3437</v>
+        <v>-0.2382</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1127</v>
+        <v>-1.1632</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6788</v>
+        <v>-1.1633</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0672</v>
+        <v>0.2365</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.746</v>
+        <v>-1.3998</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0672</v>
+        <v>0.2365</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0678</v>
+        <v>0.2462</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.746</v>
+        <v>-1.3998</v>
       </c>
       <c r="K36" t="n">
         <v>123</v>
@@ -2093,7 +2093,7 @@
         <v>106</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6782</v>
+        <v>-1.1536</v>
       </c>
       <c r="N36" t="n">
         <v>229</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.7223</v>
+        <v>-1.2001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3526</v>
+        <v>-0.2457</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1301</v>
+        <v>-1.1798</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.7223</v>
+        <v>-1.2001</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-1.2001</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9224</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-1.2001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-1.2001</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9224</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L37" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.7223</v>
+        <v>-1.2001</v>
       </c>
       <c r="N37" t="n">
-        <v>163</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7963</v>
+        <v>-1.2308</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3678</v>
+        <v>-0.252</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1596</v>
+        <v>-1.1937</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7963</v>
+        <v>-1.2308</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7963</v>
+        <v>-0.6399</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.5909</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7963</v>
+        <v>-0.6399</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.7963</v>
+        <v>-0.6399</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.5909</v>
       </c>
       <c r="K38" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7963</v>
+        <v>-1.2308</v>
       </c>
       <c r="N38" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.2659</v>
+        <v>-1.5333</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4639</v>
+        <v>-0.3139</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3466</v>
+        <v>-1.3302</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2659</v>
+        <v>-1.5333</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4012</v>
+        <v>-0.9797</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8647</v>
+        <v>-0.5536</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4012</v>
+        <v>-0.9797</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4012</v>
+        <v>-0.9797</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8647</v>
+        <v>-0.5536</v>
       </c>
       <c r="K39" t="n">
         <v>109</v>
@@ -2231,7 +2231,7 @@
         <v>54</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.2659</v>
+        <v>-1.5333</v>
       </c>
       <c r="N39" t="n">
         <v>163</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>HUNDEN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.2221</v>
+        <v>-2.6135</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6597</v>
+        <v>-0.5351</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7276</v>
+        <v>-1.8179</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.2221</v>
+        <v>-2.6135</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.5165</v>
+        <v>-1.5157</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7056</v>
+        <v>-1.0978</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.5165</v>
+        <v>-1.5157</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0397</v>
+        <v>-1.5157</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7056</v>
+        <v>-1.0978</v>
       </c>
       <c r="K40" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="L40" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.7453</v>
+        <v>-2.6135</v>
       </c>
       <c r="N40" t="n">
-        <v>284</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HUNDEN</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2401</v>
+        <v>-3.4514</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6634</v>
+        <v>-0.7067</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7348</v>
+        <v>-2.1961</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2401</v>
+        <v>-3.4514</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7496</v>
+        <v>-3.2384</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.4905</v>
+        <v>-0.213</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7496</v>
+        <v>-3.2384</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7496</v>
+        <v>-1.6838</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.4905</v>
+        <v>-0.213</v>
       </c>
       <c r="K41" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L41" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.2401</v>
+        <v>-1.8968</v>
       </c>
       <c r="N41" t="n">
-        <v>246</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1.212</v>
+        <v>1.1278</v>
       </c>
       <c r="J2" t="n">
-        <v>36.36</v>
+        <v>33.834</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5772</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>17.316</v>
+        <v>16.317</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1639</v>
+        <v>0.1842</v>
       </c>
       <c r="J4" t="n">
-        <v>4.917</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5113</v>
+        <v>-0.4522</v>
       </c>
       <c r="J5" t="n">
-        <v>-15.339</v>
+        <v>-13.566</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.76</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7869</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-23.607</v>
+        <v>-22.272</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.72</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9819</v>
+        <v>1.1567</v>
       </c>
       <c r="J7" t="n">
-        <v>29.457</v>
+        <v>34.701</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1177</v>
+        <v>-0.0567</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.531</v>
+        <v>-1.701</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.97</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1177</v>
+        <v>-0.0567</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.531</v>
+        <v>-1.701</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1772</v>
+        <v>-0.0953</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.316</v>
+        <v>-2.859</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.74</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4796</v>
+        <v>-0.3054</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.388</v>
+        <v>-9.162000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9651</v>
+        <v>0.9654</v>
       </c>
       <c r="J12" t="n">
-        <v>23.1624</v>
+        <v>23.1696</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.36</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9211</v>
+        <v>0.9248</v>
       </c>
       <c r="J13" t="n">
-        <v>22.1064</v>
+        <v>22.1952</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.25</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6599</v>
+        <v>0.6745</v>
       </c>
       <c r="J14" t="n">
-        <v>15.8376</v>
+        <v>16.188</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4245</v>
+        <v>0.485</v>
       </c>
       <c r="J15" t="n">
-        <v>10.188</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4525</v>
+        <v>-0.3777</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.86</v>
+        <v>-9.0648</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.9336</v>
       </c>
       <c r="J17" t="n">
-        <v>17.964</v>
+        <v>22.4064</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2444</v>
+        <v>0.2516</v>
       </c>
       <c r="J18" t="n">
-        <v>5.8656</v>
+        <v>6.0384</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.88</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2285</v>
+        <v>-0.1464</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.484</v>
+        <v>-3.5136</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5289</v>
+        <v>-0.3447</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.6936</v>
+        <v>-8.2728</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.45</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8109</v>
+        <v>-0.5557</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.4616</v>
+        <v>-13.3368</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1244</v>
+        <v>0.0755</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3588</v>
+        <v>2.0385</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0994</v>
+        <v>0.0527</v>
       </c>
       <c r="J23" t="n">
-        <v>2.6838</v>
+        <v>1.4229</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2215</v>
+        <v>-0.1532</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.9805</v>
+        <v>-4.1364</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.84</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2794</v>
+        <v>-0.1834</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.5438</v>
+        <v>-4.9518</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.62</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5985</v>
+        <v>-0.3959</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.1595</v>
+        <v>-10.6893</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9436</v>
+        <v>0.8602</v>
       </c>
       <c r="J27" t="n">
-        <v>25.4772</v>
+        <v>23.2254</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4699</v>
+        <v>0.4112</v>
       </c>
       <c r="J28" t="n">
-        <v>12.6873</v>
+        <v>11.1024</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2512</v>
+        <v>0.2457</v>
       </c>
       <c r="J29" t="n">
-        <v>6.7824</v>
+        <v>6.6339</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0122</v>
+        <v>0.0243</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3294</v>
+        <v>0.6561</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.76</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4723</v>
+        <v>-0.2986</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.7521</v>
+        <v>-8.062200000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1736</v>
+        <v>1.1086</v>
       </c>
       <c r="J32" t="n">
-        <v>29.34</v>
+        <v>27.715</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.23</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6347</v>
+        <v>0.6357</v>
       </c>
       <c r="J33" t="n">
-        <v>15.8675</v>
+        <v>15.8925</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.11</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2781</v>
+        <v>0.3359</v>
       </c>
       <c r="J34" t="n">
-        <v>6.9525</v>
+        <v>8.397500000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.07</v>
       </c>
       <c r="I35" t="n">
-        <v>0.158</v>
+        <v>0.2207</v>
       </c>
       <c r="J35" t="n">
-        <v>3.95</v>
+        <v>5.5175</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1141</v>
+        <v>-0.0425</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.8525</v>
+        <v>-1.0625</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3381</v>
+        <v>0.376</v>
       </c>
       <c r="J37" t="n">
-        <v>8.452500000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1313</v>
+        <v>0.1243</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2825</v>
+        <v>3.1075</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.95</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1166</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.915</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.84</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3138</v>
+        <v>-0.1939</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.845</v>
+        <v>-4.8475</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3444</v>
+        <v>-0.2144</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.609999999999999</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0865</v>
+        <v>0.7893</v>
       </c>
       <c r="J42" t="n">
-        <v>24.9895</v>
+        <v>18.1539</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9583</v>
+        <v>0.7125</v>
       </c>
       <c r="J43" t="n">
-        <v>22.0409</v>
+        <v>16.3875</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.32</v>
       </c>
       <c r="I44" t="n">
-        <v>0.798</v>
+        <v>0.6216</v>
       </c>
       <c r="J44" t="n">
-        <v>18.354</v>
+        <v>14.2968</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.17</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3947</v>
+        <v>0.4163</v>
       </c>
       <c r="J45" t="n">
-        <v>9.078099999999999</v>
+        <v>9.5749</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.01</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0883</v>
+        <v>-0.0104</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.0309</v>
+        <v>-0.2392</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.15</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3761</v>
+        <v>0.3825</v>
       </c>
       <c r="J47" t="n">
-        <v>8.6503</v>
+        <v>8.797499999999999</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.91</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1135</v>
+        <v>-0.1035</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.6105</v>
+        <v>-2.3805</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2391</v>
+        <v>-0.1791</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.4993</v>
+        <v>-4.1193</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5194</v>
+        <v>-0.3421</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.9462</v>
+        <v>-7.8683</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6894</v>
+        <v>-0.4635</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.8562</v>
+        <v>-10.6605</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.64</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4422</v>
+        <v>1.0165</v>
       </c>
       <c r="J52" t="n">
-        <v>41.8238</v>
+        <v>29.4785</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.46</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0873</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>31.5317</v>
+        <v>23.0521</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6016</v>
+        <v>0.5393</v>
       </c>
       <c r="J54" t="n">
-        <v>17.4464</v>
+        <v>15.6397</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3769</v>
+        <v>0.4111</v>
       </c>
       <c r="J55" t="n">
-        <v>10.9301</v>
+        <v>11.9219</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.01</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1003</v>
+        <v>-0.0197</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.9087</v>
+        <v>-0.5713</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.97</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0321</v>
+        <v>-0.0117</v>
       </c>
       <c r="J57" t="n">
-        <v>0.9308999999999999</v>
+        <v>-0.3393</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.77</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3221</v>
+        <v>-0.2396</v>
       </c>
       <c r="J58" t="n">
-        <v>-9.3409</v>
+        <v>-6.9484</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4031</v>
+        <v>-0.2762</v>
       </c>
       <c r="J59" t="n">
-        <v>-11.6899</v>
+        <v>-8.0098</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4821</v>
+        <v>-0.3231</v>
       </c>
       <c r="J60" t="n">
-        <v>-13.9809</v>
+        <v>-9.369899999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5542</v>
+        <v>-0.37</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.0718</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.07</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2123</v>
+        <v>0.1612</v>
       </c>
       <c r="J62" t="n">
-        <v>6.1567</v>
+        <v>4.6748</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0861</v>
+        <v>0.045</v>
       </c>
       <c r="J63" t="n">
-        <v>2.4969</v>
+        <v>1.305</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0674</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.1866</v>
+        <v>-1.9546</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.87</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2425</v>
+        <v>-0.1561</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.0325</v>
+        <v>-4.5269</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.605</v>
+        <v>-0.3999</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.545</v>
+        <v>-11.5971</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.72</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9487</v>
+        <v>0.647</v>
       </c>
       <c r="J67" t="n">
-        <v>27.5123</v>
+        <v>18.763</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.25</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3932</v>
+        <v>0.3378</v>
       </c>
       <c r="J68" t="n">
-        <v>11.4028</v>
+        <v>9.796200000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0535</v>
+        <v>0.0793</v>
       </c>
       <c r="J69" t="n">
-        <v>1.5515</v>
+        <v>2.2997</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.008</v>
+        <v>0.0266</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.232</v>
+        <v>0.7714</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3459</v>
+        <v>-0.2069</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.0311</v>
+        <v>-6.0001</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.68</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4639</v>
+        <v>1.04</v>
       </c>
       <c r="J72" t="n">
-        <v>29.278</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.47</v>
       </c>
       <c r="I73" t="n">
-        <v>1.044</v>
+        <v>0.7909</v>
       </c>
       <c r="J73" t="n">
-        <v>20.88</v>
+        <v>15.818</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.38</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.6827</v>
       </c>
       <c r="J74" t="n">
-        <v>16.382</v>
+        <v>13.654</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.34</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.6318</v>
       </c>
       <c r="J75" t="n">
-        <v>14.566</v>
+        <v>12.636</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I76" t="n">
-        <v>0.57</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>11.4</v>
+        <v>10.776</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.84</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1797</v>
+        <v>-0.1595</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.594</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.196</v>
+        <v>-0.1704</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.92</v>
+        <v>-3.408</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2446</v>
+        <v>-0.2022</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.892</v>
+        <v>-4.044</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3097</v>
+        <v>-0.2427</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.194</v>
+        <v>-4.854</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.32</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9346</v>
+        <v>-0.6518</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.692</v>
+        <v>-13.036</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.58</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3617</v>
+        <v>0.9599</v>
       </c>
       <c r="J82" t="n">
-        <v>38.1276</v>
+        <v>26.8772</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.53</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2643</v>
+        <v>0.8972</v>
       </c>
       <c r="J83" t="n">
-        <v>35.4004</v>
+        <v>25.1216</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.24</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5189</v>
       </c>
       <c r="J84" t="n">
-        <v>17.1472</v>
+        <v>14.5292</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0026</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.1756</v>
+        <v>-0.0728</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6908</v>
+        <v>-0.6315</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.3424</v>
+        <v>-17.682</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.97</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0053</v>
+        <v>-0.0311</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.1484</v>
+        <v>-0.8708</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.92</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1045</v>
+        <v>-0.0951</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.926</v>
+        <v>-2.6628</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3157</v>
+        <v>-0.2099</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.839600000000001</v>
+        <v>-5.8772</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.77</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3806</v>
+        <v>-0.249</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.6568</v>
+        <v>-6.972</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.74</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.426</v>
+        <v>-0.2781</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.928</v>
+        <v>-7.7868</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4861</v>
+        <v>0.4707</v>
       </c>
       <c r="J92" t="n">
-        <v>12.1525</v>
+        <v>11.7675</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1678</v>
+        <v>0.1513</v>
       </c>
       <c r="J93" t="n">
-        <v>4.195</v>
+        <v>3.7825</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.84</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2794</v>
+        <v>-0.1834</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.985</v>
+        <v>-4.585</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.64</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5725</v>
+        <v>-0.3772</v>
       </c>
       <c r="J95" t="n">
-        <v>-14.3125</v>
+        <v>-9.43</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.624</v>
+        <v>-0.4145</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.6</v>
+        <v>-10.3625</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.43</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1171</v>
+        <v>0.7954</v>
       </c>
       <c r="J97" t="n">
-        <v>27.9275</v>
+        <v>19.885</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.38</v>
       </c>
       <c r="I98" t="n">
-        <v>1.0114</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>25.285</v>
+        <v>18.2075</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1194</v>
+        <v>0.1705</v>
       </c>
       <c r="J99" t="n">
-        <v>2.985</v>
+        <v>4.2625</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1519</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.7975</v>
+        <v>-2.1125</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7579</v>
+        <v>-0.7081</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.9475</v>
+        <v>-17.7025</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7029</v>
+        <v>0.6485</v>
       </c>
       <c r="J102" t="n">
-        <v>20.3841</v>
+        <v>18.8065</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.16</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3085</v>
+        <v>0.3439</v>
       </c>
       <c r="J103" t="n">
-        <v>8.9465</v>
+        <v>9.973100000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2407</v>
+        <v>-0.1391</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.9803</v>
+        <v>-4.0339</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2891</v>
+        <v>-0.1718</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.383900000000001</v>
+        <v>-4.9822</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3499</v>
+        <v>-0.2137</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.1471</v>
+        <v>-6.1973</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5058</v>
+        <v>0.4142</v>
       </c>
       <c r="J107" t="n">
-        <v>14.6682</v>
+        <v>12.0118</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.12</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4211</v>
+        <v>0.3664</v>
       </c>
       <c r="J108" t="n">
-        <v>12.2119</v>
+        <v>10.6256</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2973</v>
+        <v>0.2761</v>
       </c>
       <c r="J109" t="n">
-        <v>8.621700000000001</v>
+        <v>8.0069</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1948</v>
+        <v>-0.1426</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.6492</v>
+        <v>-4.1354</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3312</v>
+        <v>-0.2738</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.604799999999999</v>
+        <v>-7.9402</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.22</v>
       </c>
       <c r="I112" t="n">
-        <v>0.431</v>
+        <v>0.4288</v>
       </c>
       <c r="J112" t="n">
-        <v>12.068</v>
+        <v>12.0064</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2314</v>
+        <v>0.2405</v>
       </c>
       <c r="J113" t="n">
-        <v>6.4792</v>
+        <v>6.734</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1167</v>
+        <v>0.1034</v>
       </c>
       <c r="J114" t="n">
-        <v>3.2676</v>
+        <v>2.8952</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.7</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5097</v>
+        <v>-0.3299</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.2716</v>
+        <v>-9.2372</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5229</v>
+        <v>-0.3394</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.6412</v>
+        <v>-9.5032</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.44</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1295</v>
+        <v>0.8044</v>
       </c>
       <c r="J117" t="n">
-        <v>31.626</v>
+        <v>22.5232</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.3</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8249</v>
+        <v>0.6153</v>
       </c>
       <c r="J118" t="n">
-        <v>23.0972</v>
+        <v>17.2284</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.16</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4673</v>
+        <v>0.4152</v>
       </c>
       <c r="J119" t="n">
-        <v>13.0844</v>
+        <v>11.6256</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.002</v>
+        <v>0.062</v>
       </c>
       <c r="J120" t="n">
-        <v>0.056</v>
+        <v>1.736</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7387</v>
+        <v>-0.6866</v>
       </c>
       <c r="J121" t="n">
-        <v>-20.6836</v>
+        <v>-19.2248</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4434</v>
+        <v>0.4405</v>
       </c>
       <c r="J122" t="n">
-        <v>12.4152</v>
+        <v>12.334</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2971</v>
+        <v>0.3262</v>
       </c>
       <c r="J123" t="n">
-        <v>8.3188</v>
+        <v>9.133599999999999</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0466</v>
+        <v>0.0392</v>
       </c>
       <c r="J124" t="n">
-        <v>1.3048</v>
+        <v>1.0976</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.87</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2746</v>
+        <v>-0.1657</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.6888</v>
+        <v>-4.6396</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5314</v>
+        <v>-0.3446</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.8792</v>
+        <v>-9.6488</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.38</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0697</v>
+        <v>0.7593</v>
       </c>
       <c r="J127" t="n">
-        <v>29.9516</v>
+        <v>21.2604</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7295</v>
+        <v>0.5432</v>
       </c>
       <c r="J128" t="n">
-        <v>20.426</v>
+        <v>15.2096</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2488</v>
+        <v>-0.2025</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.9664</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.87</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4925</v>
+        <v>-0.4395</v>
       </c>
       <c r="J130" t="n">
-        <v>-13.79</v>
+        <v>-12.306</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9782</v>
+        <v>-0.9529</v>
       </c>
       <c r="J131" t="n">
-        <v>-27.3896</v>
+        <v>-26.6812</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.93</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0533</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.2259</v>
+        <v>-1.5893</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.8</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2779</v>
+        <v>-0.2125</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.3917</v>
+        <v>-4.8875</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.75</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3774</v>
+        <v>-0.2592</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.680199999999999</v>
+        <v>-5.9616</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.7</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4579</v>
+        <v>-0.3063</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.5317</v>
+        <v>-7.0449</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5023</v>
+        <v>-0.3345</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.5529</v>
+        <v>-7.6935</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.83</v>
       </c>
       <c r="I137" t="n">
-        <v>1.7814</v>
+        <v>1.5149</v>
       </c>
       <c r="J137" t="n">
-        <v>40.9722</v>
+        <v>34.8427</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.71</v>
       </c>
       <c r="I138" t="n">
-        <v>1.5679</v>
+        <v>1.3726</v>
       </c>
       <c r="J138" t="n">
-        <v>36.0617</v>
+        <v>31.5698</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3989</v>
+        <v>0.4884</v>
       </c>
       <c r="J139" t="n">
-        <v>9.1747</v>
+        <v>11.2332</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.02</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0614</v>
+        <v>0.0195</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.4122</v>
+        <v>0.4485</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.66</v>
+        <v>-0.5964</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.18</v>
+        <v>-13.7172</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.01</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1538</v>
+        <v>0.1252</v>
       </c>
       <c r="J142" t="n">
-        <v>3.076</v>
+        <v>2.504</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.78</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2964</v>
+        <v>-0.2285</v>
       </c>
       <c r="J143" t="n">
-        <v>-5.928</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.67</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4919</v>
+        <v>-0.3307</v>
       </c>
       <c r="J144" t="n">
-        <v>-9.837999999999999</v>
+        <v>-6.614</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5214</v>
+        <v>-0.3494</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.428</v>
+        <v>-6.988</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.578</v>
+        <v>-0.3869</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.56</v>
+        <v>-7.738</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.584</v>
+        <v>1.3884</v>
       </c>
       <c r="J147" t="n">
-        <v>31.68</v>
+        <v>27.768</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.47</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0582</v>
+        <v>1.0673</v>
       </c>
       <c r="J148" t="n">
-        <v>21.164</v>
+        <v>21.346</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.37</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8101</v>
+        <v>0.9082</v>
       </c>
       <c r="J149" t="n">
-        <v>16.202</v>
+        <v>18.164</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.27</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5793</v>
+        <v>0.6866</v>
       </c>
       <c r="J150" t="n">
-        <v>11.586</v>
+        <v>13.732</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.17</v>
       </c>
       <c r="I151" t="n">
-        <v>0.3423</v>
+        <v>0.4438</v>
       </c>
       <c r="J151" t="n">
-        <v>6.846</v>
+        <v>8.875999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5684</v>
+        <v>0.6807</v>
       </c>
       <c r="J152" t="n">
-        <v>16.4836</v>
+        <v>19.7403</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1632</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.7328</v>
+        <v>-2.8188</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.92</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1822</v>
+        <v>-0.1087</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.2838</v>
+        <v>-3.1523</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2357</v>
+        <v>-0.1421</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.8353</v>
+        <v>-4.1209</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3913</v>
+        <v>-0.2457</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.3477</v>
+        <v>-7.1253</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6917</v>
+        <v>0.6632</v>
       </c>
       <c r="J157" t="n">
-        <v>20.0593</v>
+        <v>19.2328</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5646</v>
+        <v>0.5374</v>
       </c>
       <c r="J158" t="n">
-        <v>16.3734</v>
+        <v>15.5846</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2546</v>
+        <v>0.2702</v>
       </c>
       <c r="J159" t="n">
-        <v>7.3834</v>
+        <v>7.8358</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1822</v>
+        <v>0.2114</v>
       </c>
       <c r="J160" t="n">
-        <v>5.2838</v>
+        <v>6.1306</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5191</v>
+        <v>-0.4579</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.0539</v>
+        <v>-13.2791</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5361</v>
+        <v>0.6361</v>
       </c>
       <c r="J162" t="n">
-        <v>12.3303</v>
+        <v>14.6303</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2455</v>
+        <v>0.2591</v>
       </c>
       <c r="J163" t="n">
-        <v>5.6465</v>
+        <v>5.9593</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.89</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2291</v>
+        <v>-0.1401</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.2693</v>
+        <v>-3.2223</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.86</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2795</v>
+        <v>-0.1721</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.4285</v>
+        <v>-3.9583</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.62</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6141</v>
+        <v>-0.4059</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.1243</v>
+        <v>-9.335699999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.83</v>
       </c>
       <c r="I167" t="n">
-        <v>1.8253</v>
+        <v>1.5445</v>
       </c>
       <c r="J167" t="n">
-        <v>41.9819</v>
+        <v>35.5235</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.17</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4207</v>
+        <v>0.4838</v>
       </c>
       <c r="J168" t="n">
-        <v>9.6761</v>
+        <v>11.1274</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3661</v>
+        <v>0.4328</v>
       </c>
       <c r="J169" t="n">
-        <v>8.420299999999999</v>
+        <v>9.9544</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2305</v>
+        <v>-0.1497</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.3015</v>
+        <v>-3.4431</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2677</v>
+        <v>-0.187</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.1571</v>
+        <v>-4.301</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1881</v>
+        <v>0.1713</v>
       </c>
       <c r="J172" t="n">
-        <v>4.1382</v>
+        <v>3.7686</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1673</v>
+        <v>0.1454</v>
       </c>
       <c r="J173" t="n">
-        <v>3.6806</v>
+        <v>3.1988</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.71</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4629</v>
+        <v>-0.3041</v>
       </c>
       <c r="J174" t="n">
-        <v>-10.1838</v>
+        <v>-6.6902</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.3326</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.121</v>
+        <v>-7.3172</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.65</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5468</v>
+        <v>-0.361</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.0296</v>
+        <v>-7.942</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.44</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1009</v>
+        <v>1.0645</v>
       </c>
       <c r="J177" t="n">
-        <v>24.2198</v>
+        <v>23.419</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8165</v>
+        <v>0.8171</v>
       </c>
       <c r="J178" t="n">
-        <v>17.963</v>
+        <v>17.9762</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.31</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8165</v>
+        <v>0.8171</v>
       </c>
       <c r="J179" t="n">
-        <v>17.963</v>
+        <v>17.9762</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2946</v>
+        <v>0.3583</v>
       </c>
       <c r="J180" t="n">
-        <v>6.4812</v>
+        <v>7.8826</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7056</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.5232</v>
+        <v>-14.2714</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4089</v>
+        <v>0.4622</v>
       </c>
       <c r="J182" t="n">
-        <v>9.813599999999999</v>
+        <v>11.0928</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.99</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0223</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>0.5352</v>
+        <v>-0.204</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1686</v>
+        <v>-0.1237</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.0464</v>
+        <v>-2.9688</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3367</v>
+        <v>-0.2157</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.0808</v>
+        <v>-5.1768</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6773</v>
+        <v>-0.4536</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.2552</v>
+        <v>-10.8864</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.01</v>
       </c>
       <c r="I187" t="n">
-        <v>2.0112</v>
+        <v>1.7193</v>
       </c>
       <c r="J187" t="n">
-        <v>48.2688</v>
+        <v>41.2632</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9929</v>
       </c>
       <c r="J188" t="n">
-        <v>23.2128</v>
+        <v>23.8296</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2381</v>
+        <v>0.3275</v>
       </c>
       <c r="J189" t="n">
-        <v>5.7144</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.11</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2112</v>
+        <v>0.2999</v>
       </c>
       <c r="J190" t="n">
-        <v>5.0688</v>
+        <v>7.1976</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1071</v>
+        <v>-0.0252</v>
       </c>
       <c r="J191" t="n">
-        <v>-2.5704</v>
+        <v>-0.6048</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.298</v>
+        <v>0.3146</v>
       </c>
       <c r="J192" t="n">
-        <v>7.45</v>
+        <v>7.865</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.094</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.35</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.113</v>
+        <v>-0.0978</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.825</v>
+        <v>-2.445</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1882</v>
+        <v>-0.1421</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.705</v>
+        <v>-3.5525</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.46</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7924</v>
+        <v>-0.5412</v>
       </c>
       <c r="J196" t="n">
-        <v>-19.81</v>
+        <v>-13.53</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.6</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3858</v>
+        <v>1.2511</v>
       </c>
       <c r="J197" t="n">
-        <v>34.645</v>
+        <v>31.2775</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.25</v>
       </c>
       <c r="I198" t="n">
-        <v>0.605</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>15.125</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4993</v>
+        <v>0.5729</v>
       </c>
       <c r="J199" t="n">
-        <v>12.4825</v>
+        <v>14.3225</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.17</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3957</v>
+        <v>0.4741</v>
       </c>
       <c r="J200" t="n">
-        <v>9.8925</v>
+        <v>11.8525</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.1</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2073</v>
+        <v>0.287</v>
       </c>
       <c r="J201" t="n">
-        <v>5.1825</v>
+        <v>7.175</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.2</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3829</v>
+        <v>0.4381</v>
       </c>
       <c r="J202" t="n">
-        <v>11.487</v>
+        <v>13.143</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.05</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1345</v>
+        <v>0.1389</v>
       </c>
       <c r="J203" t="n">
-        <v>4.035</v>
+        <v>4.167</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.175</v>
+        <v>-0.1002</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.25</v>
+        <v>-3.006</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1934</v>
+        <v>-0.1119</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.802</v>
+        <v>-3.357</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2112</v>
+        <v>-0.1233</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.336</v>
+        <v>-3.699</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6481</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="J207" t="n">
-        <v>19.443</v>
+        <v>18.222</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.12</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4335</v>
+        <v>0.3946</v>
       </c>
       <c r="J208" t="n">
-        <v>13.005</v>
+        <v>11.838</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.04</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1686</v>
+        <v>0.1571</v>
       </c>
       <c r="J209" t="n">
-        <v>5.058</v>
+        <v>4.713</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.98</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1437</v>
+        <v>-0.101</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.311</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.82</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6297</v>
+        <v>-0.5782</v>
       </c>
       <c r="J211" t="n">
-        <v>-18.891</v>
+        <v>-17.346</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.47</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1388</v>
+        <v>1.0928</v>
       </c>
       <c r="J212" t="n">
-        <v>26.1924</v>
+        <v>25.1344</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.41</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0132</v>
+        <v>1.0103</v>
       </c>
       <c r="J213" t="n">
-        <v>23.3036</v>
+        <v>23.2369</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.25</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6314</v>
+        <v>0.6691</v>
       </c>
       <c r="J214" t="n">
-        <v>14.5222</v>
+        <v>15.3893</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.1</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2154</v>
+        <v>0.2917</v>
       </c>
       <c r="J215" t="n">
-        <v>4.9542</v>
+        <v>6.7091</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1393</v>
+        <v>-0.06</v>
       </c>
       <c r="J216" t="n">
-        <v>-3.2039</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.12</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3165</v>
+        <v>0.3383</v>
       </c>
       <c r="J217" t="n">
-        <v>7.2795</v>
+        <v>7.7809</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.99</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0375</v>
+        <v>-0.0023</v>
       </c>
       <c r="J218" t="n">
-        <v>0.8625</v>
+        <v>-0.0529</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0104</v>
+        <v>-0.0333</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.2392</v>
+        <v>-0.7659</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.71</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4731</v>
+        <v>-0.3085</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.8813</v>
+        <v>-7.0955</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7679</v>
+        <v>-0.5224</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.6617</v>
+        <v>-12.0152</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.01</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1268</v>
+        <v>0.0722</v>
       </c>
       <c r="J222" t="n">
-        <v>3.5504</v>
+        <v>2.0216</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.9</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.124</v>
+        <v>-0.1123</v>
       </c>
       <c r="J223" t="n">
-        <v>-3.472</v>
+        <v>-3.1444</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.8</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3104</v>
+        <v>-0.216</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.6912</v>
+        <v>-6.048</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.74</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4121</v>
+        <v>-0.2732</v>
       </c>
       <c r="J225" t="n">
-        <v>-11.5388</v>
+        <v>-7.6496</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.58</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6352</v>
+        <v>-0.4242</v>
       </c>
       <c r="J226" t="n">
-        <v>-17.7856</v>
+        <v>-11.8776</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.84</v>
       </c>
       <c r="I227" t="n">
-        <v>1.0665</v>
+        <v>0.9784</v>
       </c>
       <c r="J227" t="n">
-        <v>29.862</v>
+        <v>27.3952</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1706</v>
+        <v>0.1806</v>
       </c>
       <c r="J228" t="n">
-        <v>4.7768</v>
+        <v>5.0568</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.05</v>
       </c>
       <c r="I229" t="n">
-        <v>0.0494</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="J229" t="n">
-        <v>1.3832</v>
+        <v>2.1644</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.0117</v>
+        <v>0.0246</v>
       </c>
       <c r="J230" t="n">
-        <v>-0.3276</v>
+        <v>0.6888</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2058</v>
+        <v>-0.1082</v>
       </c>
       <c r="J231" t="n">
-        <v>-5.7624</v>
+        <v>-3.0296</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.39</v>
       </c>
       <c r="I232" t="n">
-        <v>1.083</v>
+        <v>1.0411</v>
       </c>
       <c r="J232" t="n">
-        <v>31.407</v>
+        <v>30.1919</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1661</v>
+        <v>0.1568</v>
       </c>
       <c r="J233" t="n">
-        <v>4.8169</v>
+        <v>4.5472</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0384</v>
+        <v>-0.0065</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.1136</v>
+        <v>-0.1885</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1451</v>
+        <v>-0.1015</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.2079</v>
+        <v>-2.9435</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7773</v>
+        <v>-0.7339</v>
       </c>
       <c r="J236" t="n">
-        <v>-22.5417</v>
+        <v>-21.2831</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.19</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3783</v>
+        <v>0.4288</v>
       </c>
       <c r="J237" t="n">
-        <v>10.9707</v>
+        <v>12.4352</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2379</v>
+        <v>0.2532</v>
       </c>
       <c r="J238" t="n">
-        <v>6.8991</v>
+        <v>7.3428</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.97</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0766</v>
+        <v>-0.048</v>
       </c>
       <c r="J239" t="n">
-        <v>-2.2214</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1235</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.5815</v>
+        <v>-2.1286</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5671</v>
+        <v>-0.3709</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.4459</v>
+        <v>-10.7561</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.9595</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>32.623</v>
+        <v>32.2354</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.25</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7063</v>
+        <v>0.6928</v>
       </c>
       <c r="J243" t="n">
-        <v>24.0142</v>
+        <v>23.5552</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.24</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6817</v>
+        <v>0.6688</v>
       </c>
       <c r="J244" t="n">
-        <v>23.1778</v>
+        <v>22.7392</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0404</v>
+        <v>0.099</v>
       </c>
       <c r="J245" t="n">
-        <v>1.3736</v>
+        <v>3.366</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.83</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.5821</v>
       </c>
       <c r="J246" t="n">
-        <v>-21.8144</v>
+        <v>-19.7914</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5654</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J247" t="n">
-        <v>19.2236</v>
+        <v>22.9806</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.93</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1488</v>
+        <v>-0.0946</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.0592</v>
+        <v>-3.2164</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1488</v>
+        <v>-0.0946</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.0592</v>
+        <v>-3.2164</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2425</v>
+        <v>-0.1498</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.244999999999999</v>
+        <v>-5.0932</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5616</v>
+        <v>-0.3675</v>
       </c>
       <c r="J251" t="n">
-        <v>-19.0944</v>
+        <v>-12.495</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.52</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2243</v>
+        <v>1.1493</v>
       </c>
       <c r="J252" t="n">
-        <v>33.0561</v>
+        <v>31.0311</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.42</v>
       </c>
       <c r="I253" t="n">
-        <v>1.018</v>
+        <v>1.0192</v>
       </c>
       <c r="J253" t="n">
-        <v>27.486</v>
+        <v>27.5184</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.36</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.9079</v>
       </c>
       <c r="J254" t="n">
-        <v>23.9112</v>
+        <v>24.5133</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.05</v>
       </c>
       <c r="I255" t="n">
-        <v>0.0542</v>
+        <v>0.1334</v>
       </c>
       <c r="J255" t="n">
-        <v>1.4634</v>
+        <v>3.6018</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.04</v>
       </c>
       <c r="I256" t="n">
-        <v>0.0215</v>
+        <v>0.1003</v>
       </c>
       <c r="J256" t="n">
-        <v>0.5805</v>
+        <v>2.7081</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.12</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3165</v>
+        <v>0.3383</v>
       </c>
       <c r="J257" t="n">
-        <v>8.545500000000001</v>
+        <v>9.1341</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0722</v>
+        <v>0.0354</v>
       </c>
       <c r="J258" t="n">
-        <v>1.9494</v>
+        <v>0.9558</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1288</v>
+        <v>-0.1085</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.4776</v>
+        <v>-2.9295</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.78</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3698</v>
+        <v>-0.2408</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.9846</v>
+        <v>-6.5016</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7916</v>
+        <v>-0.5406</v>
       </c>
       <c r="J261" t="n">
-        <v>-21.3732</v>
+        <v>-14.5962</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.4</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6805</v>
+        <v>0.8379</v>
       </c>
       <c r="J262" t="n">
-        <v>16.332</v>
+        <v>20.1096</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.87</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.2415</v>
+        <v>-0.1559</v>
       </c>
       <c r="J263" t="n">
-        <v>-5.796</v>
+        <v>-3.7416</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2415</v>
+        <v>-0.1559</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.796</v>
+        <v>-3.7416</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4158</v>
+        <v>-0.2666</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.979200000000001</v>
+        <v>-6.3984</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.61</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6173</v>
+        <v>-0.409</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.8152</v>
+        <v>-9.816000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.44</v>
       </c>
       <c r="I267" t="n">
-        <v>1.142</v>
+        <v>1.0846</v>
       </c>
       <c r="J267" t="n">
-        <v>27.408</v>
+        <v>26.0304</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7683</v>
+        <v>0.7487</v>
       </c>
       <c r="J268" t="n">
-        <v>18.4392</v>
+        <v>17.9688</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5952</v>
+        <v>0.5777</v>
       </c>
       <c r="J269" t="n">
-        <v>14.2848</v>
+        <v>13.8648</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.9</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4492</v>
+        <v>-0.3821</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.7808</v>
+        <v>-9.170400000000001</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.78</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7557</v>
+        <v>-0.706</v>
       </c>
       <c r="J271" t="n">
-        <v>-18.1368</v>
+        <v>-16.944</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.17</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3684</v>
+        <v>0.4107</v>
       </c>
       <c r="J272" t="n">
-        <v>11.052</v>
+        <v>12.321</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3382</v>
+        <v>0.3716</v>
       </c>
       <c r="J273" t="n">
-        <v>10.146</v>
+        <v>11.148</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1274</v>
+        <v>0.1105</v>
       </c>
       <c r="J274" t="n">
-        <v>3.822</v>
+        <v>3.315</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4065</v>
+        <v>-0.2591</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.195</v>
+        <v>-7.773</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.48</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7772</v>
+        <v>-0.5296</v>
       </c>
       <c r="J276" t="n">
-        <v>-23.316</v>
+        <v>-15.888</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.53</v>
       </c>
       <c r="I277" t="n">
-        <v>1.3047</v>
+        <v>1.1922</v>
       </c>
       <c r="J277" t="n">
-        <v>39.141</v>
+        <v>35.766</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.44</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1233</v>
+        <v>1.075</v>
       </c>
       <c r="J278" t="n">
-        <v>33.699</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3219</v>
+        <v>0.3677</v>
       </c>
       <c r="J279" t="n">
-        <v>9.657</v>
+        <v>11.031</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.02</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0035</v>
+        <v>0.059</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.105</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.0316</v>
+        <v>-1.0105</v>
       </c>
       <c r="J281" t="n">
-        <v>-30.948</v>
+        <v>-30.315</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.29</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8825</v>
+        <v>0.8491</v>
       </c>
       <c r="J282" t="n">
-        <v>31.77</v>
+        <v>30.5676</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.98</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1184</v>
+        <v>-0.0935</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.2624</v>
+        <v>-3.366</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.93</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3033</v>
+        <v>-0.2599</v>
       </c>
       <c r="J284" t="n">
-        <v>-10.9188</v>
+        <v>-9.356400000000001</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.91</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3663</v>
+        <v>-0.3198</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.1868</v>
+        <v>-11.5128</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.89</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4259</v>
+        <v>-0.3775</v>
       </c>
       <c r="J286" t="n">
-        <v>-15.3324</v>
+        <v>-13.59</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.85</v>
       </c>
       <c r="I287" t="n">
-        <v>1.0941</v>
+        <v>1.2519</v>
       </c>
       <c r="J287" t="n">
-        <v>39.3876</v>
+        <v>45.0684</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1582</v>
+        <v>0.2241</v>
       </c>
       <c r="J288" t="n">
-        <v>5.6952</v>
+        <v>8.067600000000001</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.08</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1221</v>
+        <v>0.1839</v>
       </c>
       <c r="J289" t="n">
-        <v>4.3956</v>
+        <v>6.6204</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.87</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3084</v>
+        <v>-0.1814</v>
       </c>
       <c r="J290" t="n">
-        <v>-11.1024</v>
+        <v>-6.5304</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.77</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4503</v>
+        <v>-0.2831</v>
       </c>
       <c r="J291" t="n">
-        <v>-16.2108</v>
+        <v>-10.1916</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4077</v>
+        <v>1.2786</v>
       </c>
       <c r="J292" t="n">
-        <v>32.3771</v>
+        <v>29.4078</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I293" t="n">
-        <v>1.3313</v>
+        <v>1.2314</v>
       </c>
       <c r="J293" t="n">
-        <v>30.6199</v>
+        <v>28.3222</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.54</v>
       </c>
       <c r="I294" t="n">
-        <v>1.1925</v>
+        <v>1.1484</v>
       </c>
       <c r="J294" t="n">
-        <v>27.4275</v>
+        <v>26.4132</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.37</v>
       </c>
       <c r="I295" t="n">
-        <v>0.7962</v>
+        <v>0.9043</v>
       </c>
       <c r="J295" t="n">
-        <v>18.3126</v>
+        <v>20.7989</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.97</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3221</v>
+        <v>-0.2338</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.4083</v>
+        <v>-5.3774</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.96</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0165</v>
+        <v>-0.0228</v>
       </c>
       <c r="J297" t="n">
-        <v>0.3795</v>
+        <v>-0.5244</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0994</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.1896</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.86</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1634</v>
+        <v>-0.1452</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.7582</v>
+        <v>-3.3396</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.54</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.6716</v>
+        <v>-0.4523</v>
       </c>
       <c r="J300" t="n">
-        <v>-15.4468</v>
+        <v>-10.4029</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.46</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7728</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.7744</v>
+        <v>-12.1141</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5147/event_5147_evp_summary.xlsx
+++ b/database/event/5147/event_5147_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.904</v>
+        <v>7.9774</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6183</v>
+        <v>1.6333</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9302</v>
+        <v>3.0073</v>
       </c>
       <c r="E2" t="n">
-        <v>7.904</v>
+        <v>7.9774</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6078</v>
+        <v>3.5292</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2962</v>
+        <v>4.4482</v>
       </c>
       <c r="H2" t="n">
-        <v>7.2254</v>
+        <v>6.7501</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7569</v>
+        <v>3.645</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2962</v>
+        <v>4.4482</v>
       </c>
       <c r="K2" t="n">
         <v>126</v>
@@ -529,7 +529,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>8.053100000000001</v>
+        <v>8.0932</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7598</v>
+        <v>6.8157</v>
       </c>
       <c r="C3" t="n">
-        <v>1.384</v>
+        <v>1.3955</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4137</v>
+        <v>2.4784</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7598</v>
+        <v>6.8157</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9444</v>
+        <v>2.8677</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8154</v>
+        <v>3.948</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8879</v>
+        <v>4.5673</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5415</v>
+        <v>2.4663</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8154</v>
+        <v>3.948</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>6.3569</v>
+        <v>6.4143</v>
       </c>
       <c r="N3" t="n">
         <v>299</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1995</v>
+        <v>6.2278</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2693</v>
+        <v>1.2751</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1608</v>
+        <v>2.2108</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1995</v>
+        <v>6.2278</v>
       </c>
       <c r="F4" t="n">
-        <v>3.182</v>
+        <v>3.1026</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0175</v>
+        <v>3.1252</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7249</v>
+        <v>5.3423</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9767</v>
+        <v>2.8848</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0175</v>
+        <v>3.1252</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -621,7 +621,7 @@
         <v>183</v>
       </c>
       <c r="M4" t="n">
-        <v>5.9942</v>
+        <v>6.01</v>
       </c>
       <c r="N4" t="n">
         <v>299</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1733</v>
+        <v>5.2366</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0592</v>
+        <v>1.0722</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6975</v>
+        <v>1.7596</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1733</v>
+        <v>5.2366</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6036</v>
+        <v>2.5215</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5697</v>
+        <v>2.7151</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6871</v>
+        <v>3.4252</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9171</v>
+        <v>1.8496</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5697</v>
+        <v>2.7151</v>
       </c>
       <c r="K5" t="n">
         <v>126</v>
@@ -667,7 +667,7 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>4.486800000000001</v>
+        <v>4.5647</v>
       </c>
       <c r="N5" t="n">
         <v>284</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1459</v>
+        <v>4.2105</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8489</v>
+        <v>0.8621</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2337</v>
+        <v>1.2925</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1459</v>
+        <v>4.2105</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7397</v>
+        <v>2.6379</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4062</v>
+        <v>1.5726</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1667</v>
+        <v>3.8091</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1665</v>
+        <v>2.0569</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4062</v>
+        <v>1.5726</v>
       </c>
       <c r="K6" t="n">
         <v>116</v>
@@ -713,7 +713,7 @@
         <v>183</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5727</v>
+        <v>3.6295</v>
       </c>
       <c r="N6" t="n">
         <v>299</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7192</v>
+        <v>3.7214</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7615</v>
+        <v>0.7619</v>
       </c>
       <c r="D7" t="n">
-        <v>1.041</v>
+        <v>1.0699</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7192</v>
+        <v>3.7214</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0806</v>
+        <v>2.9615</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.7599</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3678</v>
+        <v>4.8769</v>
       </c>
       <c r="I7" t="n">
-        <v>2.791</v>
+        <v>2.6335</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.7599</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>158</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4296</v>
+        <v>3.3934</v>
       </c>
       <c r="N7" t="n">
         <v>284</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5416</v>
+        <v>3.6384</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7251</v>
+        <v>0.7449</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9608</v>
+        <v>1.0321</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5416</v>
+        <v>3.6384</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0761</v>
+        <v>2.0831</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4655</v>
+        <v>1.5553</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0761</v>
+        <v>2.0831</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1615</v>
+        <v>2.1368</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4655</v>
+        <v>1.5553</v>
       </c>
       <c r="K8" t="n">
         <v>123</v>
@@ -805,7 +805,7 @@
         <v>106</v>
       </c>
       <c r="M8" t="n">
-        <v>3.627</v>
+        <v>3.6921</v>
       </c>
       <c r="N8" t="n">
         <v>229</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.324</v>
+        <v>3.3569</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6806</v>
+        <v>0.6873</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8626</v>
+        <v>0.9039</v>
       </c>
       <c r="E9" t="n">
-        <v>3.324</v>
+        <v>3.3569</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5231</v>
+        <v>2.4608</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8961</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4036</v>
+        <v>3.2249</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7697</v>
+        <v>1.7414</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8961</v>
       </c>
       <c r="K9" t="n">
         <v>116</v>
@@ -851,7 +851,7 @@
         <v>183</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5706</v>
+        <v>2.6375</v>
       </c>
       <c r="N9" t="n">
         <v>299</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7418</v>
+        <v>2.7562</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5614</v>
+        <v>0.5643</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5998</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7418</v>
+        <v>2.7562</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0134</v>
+        <v>1.9826</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7284</v>
+        <v>0.7736</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0134</v>
+        <v>1.9826</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0962</v>
+        <v>2.0337</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7284</v>
+        <v>0.7736</v>
       </c>
       <c r="K10" t="n">
         <v>123</v>
@@ -897,7 +897,7 @@
         <v>106</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8246</v>
+        <v>2.8073</v>
       </c>
       <c r="N10" t="n">
         <v>229</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zehN</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6903</v>
+        <v>2.5909</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5508</v>
+        <v>0.5305</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5765</v>
+        <v>0.5552</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6903</v>
+        <v>2.5909</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8453</v>
+        <v>1.2833</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.155</v>
+        <v>1.3076</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8881</v>
+        <v>1.2833</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0069</v>
+        <v>1.2833</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.155</v>
+        <v>1.3076</v>
       </c>
       <c r="K11" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="L11" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8519</v>
+        <v>2.5909</v>
       </c>
       <c r="N11" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>zehN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5333</v>
+        <v>2.4329</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5187</v>
+        <v>0.4981</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5056</v>
+        <v>0.4833</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5333</v>
+        <v>2.4329</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3397</v>
+        <v>2.5688</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1936</v>
+        <v>-0.1359</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3397</v>
+        <v>2.8974</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3397</v>
+        <v>2.9721</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1936</v>
+        <v>-0.1359</v>
       </c>
       <c r="K12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L12" t="n">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5333</v>
+        <v>2.8362</v>
       </c>
       <c r="N12" t="n">
-        <v>246</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3581</v>
+        <v>2.3176</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4828</v>
+        <v>0.4745</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4266</v>
+        <v>0.4308</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3581</v>
+        <v>2.3176</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5583</v>
+        <v>1.4426</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7998</v>
+        <v>0.875</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5583</v>
+        <v>1.4426</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5583</v>
+        <v>1.4426</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7998</v>
+        <v>0.875</v>
       </c>
       <c r="K13" t="n">
         <v>109</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3581</v>
+        <v>2.3176</v>
       </c>
       <c r="N13" t="n">
         <v>163</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3162</v>
+        <v>2.2905</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4742</v>
+        <v>0.469</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4076</v>
+        <v>0.4185</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3162</v>
+        <v>2.2905</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2929</v>
+        <v>2.2209</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0233</v>
+        <v>0.0696</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5923</v>
+        <v>2.4334</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3479</v>
+        <v>1.314</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0233</v>
+        <v>0.0696</v>
       </c>
       <c r="K14" t="n">
         <v>126</v>
@@ -1081,7 +1081,7 @@
         <v>158</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3712</v>
+        <v>1.3836</v>
       </c>
       <c r="N14" t="n">
         <v>284</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9993</v>
+        <v>2.0172</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4093</v>
+        <v>0.413</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2646</v>
+        <v>0.2941</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9993</v>
+        <v>2.0172</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1847</v>
+        <v>1.1474</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8146</v>
+        <v>0.8698</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1847</v>
+        <v>1.1474</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1847</v>
+        <v>1.1474</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8146</v>
+        <v>0.8698</v>
       </c>
       <c r="K15" t="n">
         <v>109</v>
@@ -1127,7 +1127,7 @@
         <v>54</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9993</v>
+        <v>2.0172</v>
       </c>
       <c r="N15" t="n">
         <v>163</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9327</v>
+        <v>2.0029</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3957</v>
+        <v>0.4101</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2345</v>
+        <v>0.2876</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9327</v>
+        <v>2.0029</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3214</v>
+        <v>1.2733</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6113</v>
+        <v>0.7296</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3214</v>
+        <v>1.2733</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3214</v>
+        <v>1.2733</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6113</v>
+        <v>0.7296</v>
       </c>
       <c r="K16" t="n">
         <v>113</v>
@@ -1173,7 +1173,7 @@
         <v>133</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9327</v>
+        <v>2.0029</v>
       </c>
       <c r="N16" t="n">
         <v>246</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.856</v>
+        <v>1.8888</v>
       </c>
       <c r="C17" t="n">
-        <v>0.38</v>
+        <v>0.3867</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1999</v>
+        <v>0.2356</v>
       </c>
       <c r="E17" t="n">
-        <v>1.856</v>
+        <v>1.8888</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9867</v>
+        <v>0.9318</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8693</v>
+        <v>0.957</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9867</v>
+        <v>0.9318</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9867</v>
+        <v>0.9318</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8693</v>
+        <v>0.957</v>
       </c>
       <c r="K17" t="n">
         <v>105</v>
@@ -1219,7 +1219,7 @@
         <v>56</v>
       </c>
       <c r="M17" t="n">
-        <v>1.856</v>
+        <v>1.8888</v>
       </c>
       <c r="N17" t="n">
         <v>161</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3755</v>
+        <v>1.3231</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2816</v>
+        <v>0.2709</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.017</v>
+        <v>-0.0219</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3755</v>
+        <v>1.3231</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3007</v>
+        <v>1.259</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3007</v>
+        <v>1.259</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3007</v>
+        <v>1.259</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="K18" t="n">
         <v>105</v>
@@ -1265,7 +1265,7 @@
         <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3755</v>
+        <v>1.3231</v>
       </c>
       <c r="N18" t="n">
         <v>161</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2168</v>
+        <v>1.1324</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2491</v>
+        <v>0.2319</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0887</v>
+        <v>-0.1087</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2168</v>
+        <v>1.1324</v>
       </c>
       <c r="F19" t="n">
-        <v>1.572</v>
+        <v>-0.0213</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3552</v>
+        <v>1.1537</v>
       </c>
       <c r="H19" t="n">
-        <v>1.572</v>
+        <v>-0.0213</v>
       </c>
       <c r="I19" t="n">
-        <v>1.572</v>
+        <v>-0.0213</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3552</v>
+        <v>1.1537</v>
       </c>
       <c r="K19" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L19" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2168</v>
+        <v>1.1324</v>
       </c>
       <c r="N19" t="n">
-        <v>163</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1103</v>
+        <v>1.1044</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2273</v>
+        <v>0.2261</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1368</v>
+        <v>-0.1215</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1103</v>
+        <v>1.1044</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1103</v>
+        <v>1.4889</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.3845</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1103</v>
+        <v>1.4889</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1103</v>
+        <v>1.4889</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3845</v>
       </c>
       <c r="K20" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1103</v>
+        <v>1.1044</v>
       </c>
       <c r="N20" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0747</v>
+        <v>1.0541</v>
       </c>
       <c r="C21" t="n">
-        <v>0.22</v>
+        <v>0.2158</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1528</v>
+        <v>-0.1444</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0747</v>
+        <v>1.0541</v>
       </c>
       <c r="F21" t="n">
-        <v>0.015</v>
+        <v>1.0541</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0597</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.015</v>
+        <v>1.0541</v>
       </c>
       <c r="I21" t="n">
-        <v>0.015</v>
+        <v>1.0541</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0597</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="L21" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0747</v>
+        <v>1.0541</v>
       </c>
       <c r="N21" t="n">
-        <v>246</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1483</v>
+        <v>0.1352</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.311</v>
+        <v>-0.3237</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="N22" t="n">
         <v>106</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.619</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1267</v>
+        <v>0.112</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3586</v>
+        <v>-0.3752</v>
       </c>
       <c r="E23" t="n">
-        <v>0.619</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.619</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.619</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.619</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.619</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>102</v>
@@ -1504,35 +1504,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6131</v>
+        <v>0.492</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1255</v>
+        <v>0.1007</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3612</v>
+        <v>-0.4002</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6131</v>
+        <v>0.492</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2971</v>
+        <v>0.0536</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.4384</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2971</v>
+        <v>0.0536</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2971</v>
+        <v>0.0536</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.4384</v>
       </c>
       <c r="K24" t="n">
         <v>105</v>
@@ -1541,7 +1541,7 @@
         <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6130999999999999</v>
+        <v>0.492</v>
       </c>
       <c r="N24" t="n">
         <v>161</v>
@@ -1550,35 +1550,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5161</v>
+        <v>0.4515</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1057</v>
+        <v>0.0924</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.405</v>
+        <v>-0.4187</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5161</v>
+        <v>0.4515</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08649999999999999</v>
+        <v>1.1594</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4296</v>
+        <v>-0.7079</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08649999999999999</v>
+        <v>1.1594</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08649999999999999</v>
+        <v>1.1594</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4296</v>
+        <v>-0.7079</v>
       </c>
       <c r="K25" t="n">
         <v>105</v>
@@ -1587,7 +1587,7 @@
         <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5161</v>
+        <v>0.4515</v>
       </c>
       <c r="N25" t="n">
         <v>161</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4957</v>
+        <v>0.438</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1015</v>
+        <v>0.0897</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4142</v>
+        <v>-0.4248</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4957</v>
+        <v>0.438</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4957</v>
+        <v>0.438</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4957</v>
+        <v>0.438</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4957</v>
+        <v>0.438</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4957</v>
+        <v>0.438</v>
       </c>
       <c r="N26" t="n">
         <v>106</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0261</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0053</v>
+        <v>0.0154</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6262</v>
+        <v>-0.5899</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0261</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6415</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.6154</v>
+        <v>0.9972</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6415</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6415</v>
+        <v>-0.4978</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.6154</v>
+        <v>0.9972</v>
       </c>
       <c r="K27" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L27" t="n">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="M27" t="n">
-        <v>0.02610000000000001</v>
+        <v>0.4994</v>
       </c>
       <c r="N27" t="n">
-        <v>246</v>
+        <v>299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1827</v>
+        <v>-0.0531</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0374</v>
+        <v>-0.0109</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7205</v>
+        <v>-0.6484</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1827</v>
+        <v>-0.0531</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1268</v>
+        <v>1.6116</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9441000000000001</v>
+        <v>-1.6647</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1268</v>
+        <v>1.6116</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5859</v>
+        <v>1.6116</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9441000000000001</v>
+        <v>-1.6647</v>
       </c>
       <c r="K28" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L28" t="n">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3582000000000001</v>
+        <v>-0.05310000000000015</v>
       </c>
       <c r="N28" t="n">
-        <v>299</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4504</v>
+        <v>-0.5072</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0922</v>
+        <v>-0.1038</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8413</v>
+        <v>-0.8551</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4504</v>
+        <v>-0.5072</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5404</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.0235</v>
+        <v>-1.0476</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5404</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5967</v>
+        <v>0.5543</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.0235</v>
+        <v>-1.0476</v>
       </c>
       <c r="K29" t="n">
         <v>123</v>
@@ -1771,7 +1771,7 @@
         <v>106</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4268000000000001</v>
+        <v>-0.4933000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>229</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5712</v>
+        <v>-0.6135</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.117</v>
+        <v>-0.1256</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8959</v>
+        <v>-0.9035</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5712</v>
+        <v>-0.6135</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5712</v>
+        <v>-0.6135</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5712</v>
+        <v>-0.6135</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5712</v>
+        <v>-0.6135</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5712</v>
+        <v>-0.6135</v>
       </c>
       <c r="N30" t="n">
         <v>102</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.604</v>
+        <v>-0.669</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1237</v>
+        <v>-0.137</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9107</v>
+        <v>-0.9287</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.604</v>
+        <v>-0.669</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.604</v>
+        <v>-0.669</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.604</v>
+        <v>-0.669</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.604</v>
+        <v>-0.669</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.604</v>
+        <v>-0.669</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8227</v>
+        <v>-0.8588</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1684</v>
+        <v>-0.1758</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.0094</v>
+        <v>-1.0151</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8227</v>
+        <v>-0.8588</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8227</v>
+        <v>-0.5605</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.2983</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8227</v>
+        <v>-0.5605</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8227</v>
+        <v>-0.5605</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.2983</v>
       </c>
       <c r="K32" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8227</v>
+        <v>-0.8588</v>
       </c>
       <c r="N32" t="n">
-        <v>102</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8547</v>
+        <v>-0.8822</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.175</v>
+        <v>-0.1806</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0239</v>
+        <v>-1.0258</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8547</v>
+        <v>-0.8822</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.8822</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2907</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.8822</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.8822</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2907</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L33" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8547</v>
+        <v>-0.8822</v>
       </c>
       <c r="N33" t="n">
-        <v>161</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9115</v>
+        <v>-0.9702</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1866</v>
+        <v>-0.1986</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0495</v>
+        <v>-1.0659</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9115</v>
+        <v>-0.9702</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9115</v>
+        <v>-0.9702</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9115</v>
+        <v>-0.9702</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9115</v>
+        <v>-0.9702</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9115</v>
+        <v>-0.9702</v>
       </c>
       <c r="N34" t="n">
         <v>106</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.024</v>
+        <v>-1.0515</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2097</v>
+        <v>-0.2153</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1003</v>
+        <v>-1.1029</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.024</v>
+        <v>-1.0515</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.024</v>
+        <v>-1.0515</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.024</v>
+        <v>-1.0515</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.024</v>
+        <v>-1.0515</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.024</v>
+        <v>-1.0515</v>
       </c>
       <c r="N35" t="n">
         <v>102</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1633</v>
+        <v>-1.1134</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2382</v>
+        <v>-0.228</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1632</v>
+        <v>-1.131</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1633</v>
+        <v>-1.1134</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2365</v>
+        <v>0.2718</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.3998</v>
+        <v>-1.3852</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2365</v>
+        <v>0.2718</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2462</v>
+        <v>0.2788</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.3998</v>
+        <v>-1.3852</v>
       </c>
       <c r="K36" t="n">
         <v>123</v>
@@ -2093,7 +2093,7 @@
         <v>106</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1536</v>
+        <v>-1.1064</v>
       </c>
       <c r="N36" t="n">
         <v>229</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2001</v>
+        <v>-1.1623</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2457</v>
+        <v>-0.238</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1798</v>
+        <v>-1.1533</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2001</v>
+        <v>-1.1623</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2001</v>
+        <v>-0.5462</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.6161</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2001</v>
+        <v>-0.5462</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2001</v>
+        <v>-0.5462</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.6161</v>
       </c>
       <c r="K37" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2001</v>
+        <v>-1.1623</v>
       </c>
       <c r="N37" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2308</v>
+        <v>-1.2424</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.252</v>
+        <v>-0.2544</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1937</v>
+        <v>-1.1898</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2308</v>
+        <v>-1.2424</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6399</v>
+        <v>-1.2424</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5909</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6399</v>
+        <v>-1.2424</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6399</v>
+        <v>-1.2424</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5909</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L38" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2308</v>
+        <v>-1.2424</v>
       </c>
       <c r="N38" t="n">
-        <v>163</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5333</v>
+        <v>-1.5221</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3139</v>
+        <v>-0.3116</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3302</v>
+        <v>-1.3171</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5333</v>
+        <v>-1.5221</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9797</v>
+        <v>-0.9458</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5536</v>
+        <v>-0.5763</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9797</v>
+        <v>-0.9458</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9797</v>
+        <v>-0.9458</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5536</v>
+        <v>-0.5763</v>
       </c>
       <c r="K39" t="n">
         <v>109</v>
@@ -2231,7 +2231,7 @@
         <v>54</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5333</v>
+        <v>-1.5221</v>
       </c>
       <c r="N39" t="n">
         <v>163</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.6135</v>
+        <v>-2.567</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5351</v>
+        <v>-0.5256</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.8179</v>
+        <v>-1.7928</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.6135</v>
+        <v>-2.567</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5157</v>
+        <v>-1.4988</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.0978</v>
+        <v>-1.0682</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5157</v>
+        <v>-1.4988</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5157</v>
+        <v>-1.4988</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.0978</v>
+        <v>-1.0682</v>
       </c>
       <c r="K40" t="n">
         <v>113</v>
@@ -2277,7 +2277,7 @@
         <v>133</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.6135</v>
+        <v>-2.567</v>
       </c>
       <c r="N40" t="n">
         <v>246</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.4514</v>
+        <v>-3.0511</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7067</v>
+        <v>-0.6247</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1961</v>
+        <v>-2.0131</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.4514</v>
+        <v>-3.0511</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.2384</v>
+        <v>-2.8873</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.213</v>
+        <v>-0.1638</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.2384</v>
+        <v>-2.8873</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6838</v>
+        <v>-1.5591</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.213</v>
+        <v>-0.1638</v>
       </c>
       <c r="K41" t="n">
         <v>126</v>
@@ -2323,7 +2323,7 @@
         <v>158</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8968</v>
+        <v>-1.7229</v>
       </c>
       <c r="N41" t="n">
         <v>284</v>
@@ -2429,10 +2429,10 @@
         <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1278</v>
+        <v>1.11</v>
       </c>
       <c r="J2" t="n">
-        <v>33.834</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5235</v>
       </c>
       <c r="J3" t="n">
-        <v>16.317</v>
+        <v>15.705</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1842</v>
+        <v>0.1915</v>
       </c>
       <c r="J4" t="n">
-        <v>5.526</v>
+        <v>5.745</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4522</v>
+        <v>-0.4323</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.566</v>
+        <v>-12.969</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.76</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.6911</v>
       </c>
       <c r="J6" t="n">
-        <v>-22.272</v>
+        <v>-20.733</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.72</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1567</v>
+        <v>1.1781</v>
       </c>
       <c r="J7" t="n">
-        <v>34.701</v>
+        <v>35.343</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0567</v>
+        <v>-0.0633</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.701</v>
+        <v>-1.899</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.97</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0567</v>
+        <v>-0.0633</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.701</v>
+        <v>-1.899</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0953</v>
+        <v>-0.1045</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.859</v>
+        <v>-3.135</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.74</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3054</v>
+        <v>-0.3163</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.162000000000001</v>
+        <v>-9.489000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9654</v>
+        <v>0.9083</v>
       </c>
       <c r="J12" t="n">
-        <v>23.1696</v>
+        <v>21.7992</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.36</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9248</v>
+        <v>0.8694</v>
       </c>
       <c r="J13" t="n">
-        <v>22.1952</v>
+        <v>20.8656</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.25</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6745</v>
+        <v>0.6484</v>
       </c>
       <c r="J14" t="n">
-        <v>16.188</v>
+        <v>15.5616</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.485</v>
+        <v>0.4778</v>
       </c>
       <c r="J15" t="n">
-        <v>11.64</v>
+        <v>11.4672</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3777</v>
+        <v>-0.3556</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.0648</v>
+        <v>-8.5344</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9336</v>
+        <v>0.8756</v>
       </c>
       <c r="J17" t="n">
-        <v>22.4064</v>
+        <v>21.0144</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2516</v>
+        <v>0.2515</v>
       </c>
       <c r="J18" t="n">
-        <v>6.0384</v>
+        <v>6.036</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.88</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1464</v>
+        <v>-0.1618</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.5136</v>
+        <v>-3.8832</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3447</v>
+        <v>-0.3578</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.2728</v>
+        <v>-8.587199999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.45</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5557</v>
+        <v>-0.5584</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.3368</v>
+        <v>-13.4016</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0755</v>
+        <v>0.076</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0385</v>
+        <v>2.052</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0527</v>
+        <v>0.0516</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4229</v>
+        <v>1.3932</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1532</v>
+        <v>-0.1697</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.1364</v>
+        <v>-4.5819</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.84</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1834</v>
+        <v>-0.2004</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.9518</v>
+        <v>-5.4108</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.62</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3959</v>
+        <v>-0.4078</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.6893</v>
+        <v>-11.0106</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8602</v>
+        <v>0.8433</v>
       </c>
       <c r="J27" t="n">
-        <v>23.2254</v>
+        <v>22.7691</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4112</v>
+        <v>0.4246</v>
       </c>
       <c r="J28" t="n">
-        <v>11.1024</v>
+        <v>11.4642</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2457</v>
+        <v>0.2634</v>
       </c>
       <c r="J29" t="n">
-        <v>6.6339</v>
+        <v>7.1118</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0243</v>
+        <v>0.0375</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6561</v>
+        <v>1.0125</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.76</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2986</v>
+        <v>-0.3071</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.062200000000001</v>
+        <v>-8.291700000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1086</v>
+        <v>1.0904</v>
       </c>
       <c r="J32" t="n">
-        <v>27.715</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.23</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6357</v>
+        <v>0.6121</v>
       </c>
       <c r="J33" t="n">
-        <v>15.8925</v>
+        <v>15.3025</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.11</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3359</v>
+        <v>0.3397</v>
       </c>
       <c r="J34" t="n">
-        <v>8.397500000000001</v>
+        <v>8.4925</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.07</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2207</v>
+        <v>0.2327</v>
       </c>
       <c r="J35" t="n">
-        <v>5.5175</v>
+        <v>5.8175</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0425</v>
+        <v>-0.0293</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.0625</v>
+        <v>-0.7325</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.376</v>
+        <v>0.3729</v>
       </c>
       <c r="J37" t="n">
-        <v>9.4</v>
+        <v>9.3225</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1243</v>
+        <v>0.1305</v>
       </c>
       <c r="J38" t="n">
-        <v>3.1075</v>
+        <v>3.2625</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.95</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0834</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.81</v>
+        <v>-2.085</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.84</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1939</v>
+        <v>-0.2084</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.8475</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2144</v>
+        <v>-0.2289</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.36</v>
+        <v>-5.7225</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7893</v>
+        <v>0.8753</v>
       </c>
       <c r="J42" t="n">
-        <v>18.1539</v>
+        <v>20.1319</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7125</v>
+        <v>0.7919</v>
       </c>
       <c r="J43" t="n">
-        <v>16.3875</v>
+        <v>18.2137</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.32</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6216</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>14.2968</v>
+        <v>15.916</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.17</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4163</v>
+        <v>0.4614</v>
       </c>
       <c r="J45" t="n">
-        <v>9.5749</v>
+        <v>10.6122</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.01</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0104</v>
+        <v>0.0146</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.2392</v>
+        <v>0.3358</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.15</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3825</v>
+        <v>0.3985</v>
       </c>
       <c r="J47" t="n">
-        <v>8.797499999999999</v>
+        <v>9.1655</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.91</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1035</v>
+        <v>-0.1205</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.3805</v>
+        <v>-2.7715</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1791</v>
+        <v>-0.1971</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.1193</v>
+        <v>-4.5333</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3421</v>
+        <v>-0.3575</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.8683</v>
+        <v>-8.2225</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4635</v>
+        <v>-0.4731</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.6605</v>
+        <v>-10.8813</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.64</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0165</v>
+        <v>1.1206</v>
       </c>
       <c r="J52" t="n">
-        <v>29.4785</v>
+        <v>32.4974</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.46</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.8829</v>
       </c>
       <c r="J53" t="n">
-        <v>23.0521</v>
+        <v>25.6041</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5393</v>
+        <v>0.6014</v>
       </c>
       <c r="J54" t="n">
-        <v>15.6397</v>
+        <v>17.4406</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4111</v>
+        <v>0.4567</v>
       </c>
       <c r="J55" t="n">
-        <v>11.9219</v>
+        <v>13.2443</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.01</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0197</v>
+        <v>0.008</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.5713</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0117</v>
+        <v>-0.0285</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.3393</v>
+        <v>-0.8265</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.77</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2396</v>
+        <v>-0.2593</v>
       </c>
       <c r="J58" t="n">
-        <v>-6.9484</v>
+        <v>-7.5197</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2762</v>
+        <v>-0.2954</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.0098</v>
+        <v>-8.566599999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3231</v>
+        <v>-0.3409</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.369899999999999</v>
+        <v>-9.886100000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.37</v>
+        <v>-0.386</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.73</v>
+        <v>-11.194</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.07</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1612</v>
+        <v>0.1655</v>
       </c>
       <c r="J62" t="n">
-        <v>4.6748</v>
+        <v>4.7995</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.045</v>
+        <v>0.0459</v>
       </c>
       <c r="J63" t="n">
-        <v>1.305</v>
+        <v>1.3311</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0674</v>
+        <v>-0.0796</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.9546</v>
+        <v>-2.3084</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.87</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1561</v>
+        <v>-0.1719</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.5269</v>
+        <v>-4.9851</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3999</v>
+        <v>-0.411</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.5971</v>
+        <v>-11.919</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.72</v>
       </c>
       <c r="I67" t="n">
-        <v>0.647</v>
+        <v>0.7408</v>
       </c>
       <c r="J67" t="n">
-        <v>18.763</v>
+        <v>21.4832</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.25</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3378</v>
+        <v>0.3588</v>
       </c>
       <c r="J68" t="n">
-        <v>9.796200000000001</v>
+        <v>10.4052</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0793</v>
+        <v>0.0951</v>
       </c>
       <c r="J69" t="n">
-        <v>2.2997</v>
+        <v>2.7579</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0266</v>
+        <v>0.0392</v>
       </c>
       <c r="J70" t="n">
-        <v>0.7714</v>
+        <v>1.1368</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2069</v>
+        <v>-0.2163</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.0001</v>
+        <v>-6.2727</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.68</v>
       </c>
       <c r="I72" t="n">
-        <v>1.04</v>
+        <v>1.1501</v>
       </c>
       <c r="J72" t="n">
-        <v>20.8</v>
+        <v>23.002</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.47</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7909</v>
+        <v>0.8821</v>
       </c>
       <c r="J73" t="n">
-        <v>15.818</v>
+        <v>17.642</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.38</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6827</v>
+        <v>0.7633</v>
       </c>
       <c r="J74" t="n">
-        <v>13.654</v>
+        <v>15.266</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.34</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6318</v>
+        <v>0.7073</v>
       </c>
       <c r="J75" t="n">
-        <v>12.636</v>
+        <v>14.146</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>10.776</v>
+        <v>12.086</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.84</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1595</v>
+        <v>-0.182</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.19</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1704</v>
+        <v>-0.1927</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.408</v>
+        <v>-3.854</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2022</v>
+        <v>-0.2241</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.044</v>
+        <v>-4.482</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2427</v>
+        <v>-0.2637</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.854</v>
+        <v>-5.274</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.32</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6518</v>
+        <v>-0.6508</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.036</v>
+        <v>-13.016</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.58</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9599</v>
+        <v>1.0572</v>
       </c>
       <c r="J82" t="n">
-        <v>26.8772</v>
+        <v>29.6016</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.53</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8972</v>
+        <v>0.9902</v>
       </c>
       <c r="J83" t="n">
-        <v>25.1216</v>
+        <v>27.7256</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.24</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5189</v>
+        <v>0.5767</v>
       </c>
       <c r="J84" t="n">
-        <v>14.5292</v>
+        <v>16.1476</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0026</v>
+        <v>0.02</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.0728</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6315</v>
+        <v>-0.5849</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.682</v>
+        <v>-16.3772</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.97</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0311</v>
+        <v>-0.0437</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.8708</v>
+        <v>-1.2236</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.92</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0951</v>
+        <v>-0.111</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.6628</v>
+        <v>-3.108</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2099</v>
+        <v>-0.2277</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.8772</v>
+        <v>-6.3756</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.77</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.249</v>
+        <v>-0.2664</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.972</v>
+        <v>-7.4592</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.74</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2781</v>
+        <v>-0.2949</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.7868</v>
+        <v>-8.257199999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4707</v>
+        <v>0.5143</v>
       </c>
       <c r="J92" t="n">
-        <v>11.7675</v>
+        <v>12.8575</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1513</v>
+        <v>0.1502</v>
       </c>
       <c r="J93" t="n">
-        <v>3.7825</v>
+        <v>3.755</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.84</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1834</v>
+        <v>-0.2004</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.585</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.64</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3772</v>
+        <v>-0.39</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.43</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4145</v>
+        <v>-0.4256</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.3625</v>
+        <v>-10.64</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.43</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7954</v>
+        <v>0.8754</v>
       </c>
       <c r="J97" t="n">
-        <v>19.885</v>
+        <v>21.885</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.38</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>18.2075</v>
+        <v>20.0725</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1705</v>
+        <v>0.1821</v>
       </c>
       <c r="J99" t="n">
-        <v>4.2625</v>
+        <v>4.5525</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0801</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.1125</v>
+        <v>-2.0025</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7081</v>
+        <v>-0.658</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.7025</v>
+        <v>-16.45</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6485</v>
+        <v>0.7248</v>
       </c>
       <c r="J102" t="n">
-        <v>18.8065</v>
+        <v>21.0192</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.16</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3439</v>
+        <v>0.3555</v>
       </c>
       <c r="J103" t="n">
-        <v>9.973100000000001</v>
+        <v>10.3095</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1391</v>
+        <v>-0.1507</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.0339</v>
+        <v>-4.3703</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1718</v>
+        <v>-0.1841</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.9822</v>
+        <v>-5.3389</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2137</v>
+        <v>-0.2261</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.1973</v>
+        <v>-6.5569</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4142</v>
+        <v>0.4505</v>
       </c>
       <c r="J107" t="n">
-        <v>12.0118</v>
+        <v>13.0645</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.12</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3664</v>
+        <v>0.3824</v>
       </c>
       <c r="J108" t="n">
-        <v>10.6256</v>
+        <v>11.0896</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2761</v>
+        <v>0.278</v>
       </c>
       <c r="J109" t="n">
-        <v>8.0069</v>
+        <v>8.061999999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1426</v>
+        <v>-0.1441</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.1354</v>
+        <v>-4.1789</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2738</v>
+        <v>-0.2691</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.9402</v>
+        <v>-7.8039</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.22</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4288</v>
+        <v>0.4706</v>
       </c>
       <c r="J112" t="n">
-        <v>12.0064</v>
+        <v>13.1768</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2405</v>
+        <v>0.2434</v>
       </c>
       <c r="J113" t="n">
-        <v>6.734</v>
+        <v>6.8152</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1034</v>
+        <v>0.1083</v>
       </c>
       <c r="J114" t="n">
-        <v>2.8952</v>
+        <v>3.0324</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.7</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3299</v>
+        <v>-0.3427</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.2372</v>
+        <v>-9.595599999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3394</v>
+        <v>-0.3519</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.5032</v>
+        <v>-9.853199999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.44</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8044</v>
+        <v>0.886</v>
       </c>
       <c r="J117" t="n">
-        <v>22.5232</v>
+        <v>24.808</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.3</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6153</v>
+        <v>0.6803</v>
       </c>
       <c r="J118" t="n">
-        <v>17.2284</v>
+        <v>19.0484</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.16</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4152</v>
+        <v>0.456</v>
       </c>
       <c r="J119" t="n">
-        <v>11.6256</v>
+        <v>12.768</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.062</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>1.736</v>
+        <v>2.1784</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6866</v>
+        <v>-0.6382</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.2248</v>
+        <v>-17.8696</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4405</v>
+        <v>0.4864</v>
       </c>
       <c r="J122" t="n">
-        <v>12.334</v>
+        <v>13.6192</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3262</v>
+        <v>0.3301</v>
       </c>
       <c r="J123" t="n">
-        <v>9.133599999999999</v>
+        <v>9.242800000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0392</v>
+        <v>0.0444</v>
       </c>
       <c r="J124" t="n">
-        <v>1.0976</v>
+        <v>1.2432</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.87</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1657</v>
+        <v>-0.1793</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.6396</v>
+        <v>-5.0204</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3446</v>
+        <v>-0.356</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.6488</v>
+        <v>-9.968</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.38</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7593</v>
+        <v>0.8303</v>
       </c>
       <c r="J127" t="n">
-        <v>21.2604</v>
+        <v>23.2484</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5432</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>15.2096</v>
+        <v>16.6404</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2025</v>
+        <v>-0.2039</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.67</v>
+        <v>-5.7092</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.87</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4395</v>
+        <v>-0.4234</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.306</v>
+        <v>-11.8552</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9529</v>
+        <v>-0.8767</v>
       </c>
       <c r="J131" t="n">
-        <v>-26.6812</v>
+        <v>-24.5476</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.93</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0876</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.5893</v>
+        <v>-2.0148</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.8</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2125</v>
+        <v>-0.232</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.8875</v>
+        <v>-5.336</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.75</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2592</v>
+        <v>-0.2783</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.9616</v>
+        <v>-6.4009</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.7</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3063</v>
+        <v>-0.3242</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.0449</v>
+        <v>-7.4566</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3345</v>
+        <v>-0.3516</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.6935</v>
+        <v>-8.0868</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.83</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5149</v>
+        <v>1.5057</v>
       </c>
       <c r="J137" t="n">
-        <v>34.8427</v>
+        <v>34.6311</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.71</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3726</v>
+        <v>1.3557</v>
       </c>
       <c r="J138" t="n">
-        <v>31.5698</v>
+        <v>31.1811</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4884</v>
+        <v>0.4854</v>
       </c>
       <c r="J139" t="n">
-        <v>11.2332</v>
+        <v>11.1642</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.02</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0195</v>
+        <v>0.0481</v>
       </c>
       <c r="J140" t="n">
-        <v>0.4485</v>
+        <v>1.1063</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5964</v>
+        <v>-0.55</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.7172</v>
+        <v>-12.65</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.01</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1252</v>
+        <v>0.1072</v>
       </c>
       <c r="J142" t="n">
-        <v>2.504</v>
+        <v>2.144</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.78</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2285</v>
+        <v>-0.2486</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.57</v>
+        <v>-4.972</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.67</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3307</v>
+        <v>-0.3486</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.614</v>
+        <v>-6.972</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3494</v>
+        <v>-0.3666</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.988</v>
+        <v>-7.332</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3869</v>
+        <v>-0.4024</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.738</v>
+        <v>-8.048</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3884</v>
+        <v>1.3758</v>
       </c>
       <c r="J147" t="n">
-        <v>27.768</v>
+        <v>27.516</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.47</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0673</v>
+        <v>1.0292</v>
       </c>
       <c r="J148" t="n">
-        <v>21.346</v>
+        <v>20.584</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.37</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9082</v>
+        <v>0.8617</v>
       </c>
       <c r="J149" t="n">
-        <v>18.164</v>
+        <v>17.234</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.27</v>
       </c>
       <c r="I150" t="n">
-        <v>0.6866</v>
+        <v>0.6661</v>
       </c>
       <c r="J150" t="n">
-        <v>13.732</v>
+        <v>13.322</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.17</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4438</v>
+        <v>0.4491</v>
       </c>
       <c r="J151" t="n">
-        <v>8.875999999999999</v>
+        <v>8.981999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6807</v>
+        <v>0.653</v>
       </c>
       <c r="J152" t="n">
-        <v>19.7403</v>
+        <v>18.937</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1093</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.8188</v>
+        <v>-3.1697</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.92</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1087</v>
+        <v>-0.1213</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.1523</v>
+        <v>-3.5177</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1421</v>
+        <v>-0.1558</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.1209</v>
+        <v>-4.5182</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2457</v>
+        <v>-0.2597</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.1253</v>
+        <v>-7.5313</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6632</v>
+        <v>0.6311</v>
       </c>
       <c r="J157" t="n">
-        <v>19.2328</v>
+        <v>18.3019</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5374</v>
+        <v>0.519</v>
       </c>
       <c r="J158" t="n">
-        <v>15.5846</v>
+        <v>15.051</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2702</v>
+        <v>0.2741</v>
       </c>
       <c r="J159" t="n">
-        <v>7.8358</v>
+        <v>7.9489</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2114</v>
+        <v>0.2185</v>
       </c>
       <c r="J160" t="n">
-        <v>6.1306</v>
+        <v>6.3365</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4579</v>
+        <v>-0.4363</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.2791</v>
+        <v>-12.6527</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6361</v>
+        <v>0.6113</v>
       </c>
       <c r="J162" t="n">
-        <v>14.6303</v>
+        <v>14.0599</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2591</v>
+        <v>0.2617</v>
       </c>
       <c r="J163" t="n">
-        <v>5.9593</v>
+        <v>6.0191</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.89</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1401</v>
+        <v>-0.1543</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.2223</v>
+        <v>-3.5489</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.86</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1721</v>
+        <v>-0.1868</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.9583</v>
+        <v>-4.2964</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.62</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4059</v>
+        <v>-0.4157</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.335699999999999</v>
+        <v>-9.5611</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.83</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5445</v>
+        <v>1.5319</v>
       </c>
       <c r="J167" t="n">
-        <v>35.5235</v>
+        <v>35.2337</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.17</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4838</v>
+        <v>0.4769</v>
       </c>
       <c r="J168" t="n">
-        <v>11.1274</v>
+        <v>10.9687</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4328</v>
+        <v>0.4307</v>
       </c>
       <c r="J169" t="n">
-        <v>9.9544</v>
+        <v>9.9061</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1497</v>
+        <v>-0.1384</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.4431</v>
+        <v>-3.1832</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.187</v>
+        <v>-0.175</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.301</v>
+        <v>-4.025</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1713</v>
+        <v>0.1649</v>
       </c>
       <c r="J172" t="n">
-        <v>3.7686</v>
+        <v>3.6278</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1454</v>
+        <v>0.139</v>
       </c>
       <c r="J173" t="n">
-        <v>3.1988</v>
+        <v>3.058</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.71</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3041</v>
+        <v>-0.3207</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.6902</v>
+        <v>-7.0554</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3326</v>
+        <v>-0.3483</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.3172</v>
+        <v>-7.6626</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.65</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.361</v>
+        <v>-0.3756</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.942</v>
+        <v>-8.263199999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.44</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0645</v>
+        <v>1.0176</v>
       </c>
       <c r="J177" t="n">
-        <v>23.419</v>
+        <v>22.3872</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8171</v>
+        <v>0.7735</v>
       </c>
       <c r="J178" t="n">
-        <v>17.9762</v>
+        <v>17.017</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.31</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8171</v>
+        <v>0.7735</v>
       </c>
       <c r="J179" t="n">
-        <v>17.9762</v>
+        <v>17.017</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3583</v>
+        <v>0.3615</v>
       </c>
       <c r="J180" t="n">
-        <v>7.8826</v>
+        <v>7.953</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.602</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.2714</v>
+        <v>-13.244</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4622</v>
+        <v>0.4474</v>
       </c>
       <c r="J182" t="n">
-        <v>11.0928</v>
+        <v>10.7376</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.99</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="J183" t="n">
-        <v>-0.204</v>
+        <v>-0.384</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1237</v>
+        <v>-0.1389</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.9688</v>
+        <v>-3.3336</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2157</v>
+        <v>-0.2321</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.1768</v>
+        <v>-5.5704</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4536</v>
+        <v>-0.4625</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.8864</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.01</v>
       </c>
       <c r="I187" t="n">
-        <v>1.7193</v>
+        <v>1.7199</v>
       </c>
       <c r="J187" t="n">
-        <v>41.2632</v>
+        <v>41.2776</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9929</v>
+        <v>0.9418</v>
       </c>
       <c r="J188" t="n">
-        <v>23.8296</v>
+        <v>22.6032</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3275</v>
+        <v>0.3401</v>
       </c>
       <c r="J189" t="n">
-        <v>7.86</v>
+        <v>8.1624</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.11</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2999</v>
+        <v>0.3147</v>
       </c>
       <c r="J190" t="n">
-        <v>7.1976</v>
+        <v>7.5528</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0252</v>
+        <v>0.0042</v>
       </c>
       <c r="J191" t="n">
-        <v>-0.6048</v>
+        <v>0.1008</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3146</v>
+        <v>0.307</v>
       </c>
       <c r="J192" t="n">
-        <v>7.865</v>
+        <v>7.675</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.1008</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.15</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0978</v>
+        <v>-0.1131</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.445</v>
+        <v>-2.8275</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1421</v>
+        <v>-0.1585</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.5525</v>
+        <v>-3.9625</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.46</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5412</v>
+        <v>-0.5456</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.53</v>
+        <v>-13.64</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.6</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2511</v>
+        <v>1.2245</v>
       </c>
       <c r="J197" t="n">
-        <v>31.2775</v>
+        <v>30.6125</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.25</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.6432</v>
       </c>
       <c r="J198" t="n">
-        <v>16.67</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5729</v>
+        <v>0.5592</v>
       </c>
       <c r="J199" t="n">
-        <v>14.3225</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.17</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4741</v>
+        <v>0.4702</v>
       </c>
       <c r="J200" t="n">
-        <v>11.8525</v>
+        <v>11.755</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.1</v>
       </c>
       <c r="I201" t="n">
-        <v>0.287</v>
+        <v>0.2995</v>
       </c>
       <c r="J201" t="n">
-        <v>7.175</v>
+        <v>7.4875</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.2</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4381</v>
+        <v>0.4333</v>
       </c>
       <c r="J202" t="n">
-        <v>13.143</v>
+        <v>12.999</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.05</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1389</v>
+        <v>0.1476</v>
       </c>
       <c r="J203" t="n">
-        <v>4.167</v>
+        <v>4.428</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1002</v>
+        <v>-0.1117</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.006</v>
+        <v>-3.351</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1119</v>
+        <v>-0.1238</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.357</v>
+        <v>-3.714</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1233</v>
+        <v>-0.1356</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.699</v>
+        <v>-4.068</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5778</v>
       </c>
       <c r="J207" t="n">
-        <v>18.222</v>
+        <v>17.334</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.12</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3946</v>
+        <v>0.3862</v>
       </c>
       <c r="J208" t="n">
-        <v>11.838</v>
+        <v>11.586</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.04</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1571</v>
+        <v>0.1639</v>
       </c>
       <c r="J209" t="n">
-        <v>4.713</v>
+        <v>4.917</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.98</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.101</v>
+        <v>-0.1045</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.03</v>
+        <v>-3.135</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.82</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5782</v>
+        <v>-0.5475</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.346</v>
+        <v>-16.425</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.47</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0928</v>
+        <v>1.0531</v>
       </c>
       <c r="J212" t="n">
-        <v>25.1344</v>
+        <v>24.2213</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.41</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0103</v>
+        <v>0.9569</v>
       </c>
       <c r="J213" t="n">
-        <v>23.2369</v>
+        <v>22.0087</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.25</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6691</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="J214" t="n">
-        <v>15.3893</v>
+        <v>14.8281</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.1</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2917</v>
+        <v>0.3027</v>
       </c>
       <c r="J215" t="n">
-        <v>6.7091</v>
+        <v>6.9621</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.06</v>
+        <v>-0.0415</v>
       </c>
       <c r="J216" t="n">
-        <v>-1.38</v>
+        <v>-0.9545</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.12</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3383</v>
+        <v>0.3288</v>
       </c>
       <c r="J217" t="n">
-        <v>7.7809</v>
+        <v>7.5624</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.99</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0023</v>
+        <v>-0.0112</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.0529</v>
+        <v>-0.2576</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0333</v>
+        <v>-0.0454</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.7659</v>
+        <v>-1.0442</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.71</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3085</v>
+        <v>-0.3242</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.0955</v>
+        <v>-7.4566</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5224</v>
+        <v>-0.528</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.0152</v>
+        <v>-12.144</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.01</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0722</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>2.0216</v>
+        <v>1.8536</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.9</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1123</v>
+        <v>-0.1301</v>
       </c>
       <c r="J223" t="n">
-        <v>-3.1444</v>
+        <v>-3.6428</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.8</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.216</v>
+        <v>-0.2346</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.048</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.74</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2732</v>
+        <v>-0.2911</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.6496</v>
+        <v>-8.1508</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.58</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4242</v>
+        <v>-0.4363</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.8776</v>
+        <v>-12.2164</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.84</v>
       </c>
       <c r="I227" t="n">
-        <v>0.9784</v>
+        <v>0.956</v>
       </c>
       <c r="J227" t="n">
-        <v>27.3952</v>
+        <v>26.768</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1806</v>
+        <v>0.1986</v>
       </c>
       <c r="J228" t="n">
-        <v>5.0568</v>
+        <v>5.5608</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.05</v>
       </c>
       <c r="I229" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0935</v>
       </c>
       <c r="J229" t="n">
-        <v>2.1644</v>
+        <v>2.618</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0246</v>
+        <v>0.0377</v>
       </c>
       <c r="J230" t="n">
-        <v>0.6888</v>
+        <v>1.0556</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1082</v>
+        <v>-0.1146</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.0296</v>
+        <v>-3.2088</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.39</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0411</v>
+        <v>0.979</v>
       </c>
       <c r="J232" t="n">
-        <v>30.1919</v>
+        <v>28.391</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1568</v>
+        <v>0.1637</v>
       </c>
       <c r="J233" t="n">
-        <v>4.5472</v>
+        <v>4.7473</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0065</v>
+        <v>-0.0044</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.1885</v>
+        <v>-0.1276</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1015</v>
+        <v>-0.1049</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.9435</v>
+        <v>-3.0421</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7339</v>
+        <v>-0.6852</v>
       </c>
       <c r="J236" t="n">
-        <v>-21.2831</v>
+        <v>-19.8708</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.19</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4288</v>
+        <v>0.4229</v>
       </c>
       <c r="J237" t="n">
-        <v>12.4352</v>
+        <v>12.2641</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2532</v>
+        <v>0.2575</v>
       </c>
       <c r="J238" t="n">
-        <v>7.3428</v>
+        <v>7.4675</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.97</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.048</v>
+        <v>-0.0567</v>
       </c>
       <c r="J239" t="n">
-        <v>-1.392</v>
+        <v>-1.6443</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.1286</v>
+        <v>-2.4418</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3709</v>
+        <v>-0.3818</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.7561</v>
+        <v>-11.0722</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.8869</v>
       </c>
       <c r="J242" t="n">
-        <v>32.2354</v>
+        <v>30.1546</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.25</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6928</v>
+        <v>0.661</v>
       </c>
       <c r="J243" t="n">
-        <v>23.5552</v>
+        <v>22.474</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.24</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6688</v>
+        <v>0.6397</v>
       </c>
       <c r="J244" t="n">
-        <v>22.7392</v>
+        <v>21.7498</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.099</v>
+        <v>0.1143</v>
       </c>
       <c r="J245" t="n">
-        <v>3.366</v>
+        <v>3.8862</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.83</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5821</v>
+        <v>-0.5451</v>
       </c>
       <c r="J246" t="n">
-        <v>-19.7914</v>
+        <v>-18.5334</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6466</v>
       </c>
       <c r="J247" t="n">
-        <v>22.9806</v>
+        <v>21.9844</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.93</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0946</v>
+        <v>-0.1073</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.2164</v>
+        <v>-3.6482</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0946</v>
+        <v>-0.1073</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.2164</v>
+        <v>-3.6482</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1498</v>
+        <v>-0.1644</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.0932</v>
+        <v>-5.5896</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3675</v>
+        <v>-0.379</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.495</v>
+        <v>-12.886</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.52</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1493</v>
+        <v>1.116</v>
       </c>
       <c r="J252" t="n">
-        <v>31.0311</v>
+        <v>30.132</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.42</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0192</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J253" t="n">
-        <v>27.5184</v>
+        <v>26.1414</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.36</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9079</v>
+        <v>0.8572</v>
       </c>
       <c r="J254" t="n">
-        <v>24.5133</v>
+        <v>23.1444</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.05</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1334</v>
+        <v>0.1563</v>
       </c>
       <c r="J255" t="n">
-        <v>3.6018</v>
+        <v>4.2201</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.04</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1003</v>
+        <v>0.1246</v>
       </c>
       <c r="J256" t="n">
-        <v>2.7081</v>
+        <v>3.3642</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.12</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3383</v>
+        <v>0.3288</v>
       </c>
       <c r="J257" t="n">
-        <v>9.1341</v>
+        <v>8.877599999999999</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0354</v>
+        <v>0.0256</v>
       </c>
       <c r="J258" t="n">
-        <v>0.9558</v>
+        <v>0.6912</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1085</v>
+        <v>-0.1243</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.9295</v>
+        <v>-3.3561</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.78</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2408</v>
+        <v>-0.258</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.5016</v>
+        <v>-6.966</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5406</v>
+        <v>-0.5451</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.5962</v>
+        <v>-14.7177</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.4</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8379</v>
+        <v>0.7883</v>
       </c>
       <c r="J262" t="n">
-        <v>20.1096</v>
+        <v>18.9192</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.87</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1559</v>
+        <v>-0.1717</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.7416</v>
+        <v>-4.1208</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1559</v>
+        <v>-0.1717</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.7416</v>
+        <v>-4.1208</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2666</v>
+        <v>-0.282</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.3984</v>
+        <v>-6.768</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.61</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.409</v>
+        <v>-0.4197</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.816000000000001</v>
+        <v>-10.0728</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.44</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0846</v>
+        <v>1.0372</v>
       </c>
       <c r="J267" t="n">
-        <v>26.0304</v>
+        <v>24.8928</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7487</v>
+        <v>0.7088</v>
       </c>
       <c r="J268" t="n">
-        <v>17.9688</v>
+        <v>17.0112</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5777</v>
+        <v>0.5572</v>
       </c>
       <c r="J269" t="n">
-        <v>13.8648</v>
+        <v>13.3728</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.9</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3821</v>
+        <v>-0.3652</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.170400000000001</v>
+        <v>-8.764799999999999</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.78</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.706</v>
+        <v>-0.6565</v>
       </c>
       <c r="J271" t="n">
-        <v>-16.944</v>
+        <v>-15.756</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.17</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4107</v>
+        <v>0.4022</v>
       </c>
       <c r="J272" t="n">
-        <v>12.321</v>
+        <v>12.066</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3716</v>
+        <v>0.3657</v>
       </c>
       <c r="J273" t="n">
-        <v>11.148</v>
+        <v>10.971</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1105</v>
+        <v>0.1134</v>
       </c>
       <c r="J274" t="n">
-        <v>3.315</v>
+        <v>3.402</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2591</v>
+        <v>-0.2742</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.773</v>
+        <v>-8.226000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.48</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5296</v>
+        <v>-0.5337</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.888</v>
+        <v>-16.011</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.53</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1922</v>
+        <v>1.1563</v>
       </c>
       <c r="J277" t="n">
-        <v>35.766</v>
+        <v>34.689</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.44</v>
       </c>
       <c r="I278" t="n">
-        <v>1.075</v>
+        <v>1.0279</v>
       </c>
       <c r="J278" t="n">
-        <v>32.25</v>
+        <v>30.837</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3677</v>
+        <v>0.368</v>
       </c>
       <c r="J279" t="n">
-        <v>11.031</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.02</v>
       </c>
       <c r="I280" t="n">
-        <v>0.059</v>
+        <v>0.0757</v>
       </c>
       <c r="J280" t="n">
-        <v>1.77</v>
+        <v>2.271</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.0105</v>
+        <v>-0.9213</v>
       </c>
       <c r="J281" t="n">
-        <v>-30.315</v>
+        <v>-27.639</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.29</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8491</v>
+        <v>0.7876</v>
       </c>
       <c r="J282" t="n">
-        <v>30.5676</v>
+        <v>28.3536</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.98</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0935</v>
+        <v>-0.0994</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.366</v>
+        <v>-3.5784</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.93</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2599</v>
+        <v>-0.2595</v>
       </c>
       <c r="J284" t="n">
-        <v>-9.356400000000001</v>
+        <v>-9.342000000000001</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.91</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3198</v>
+        <v>-0.3151</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.5128</v>
+        <v>-11.3436</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.89</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3775</v>
+        <v>-0.3682</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.59</v>
+        <v>-13.2552</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.85</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2519</v>
+        <v>1.2399</v>
       </c>
       <c r="J287" t="n">
-        <v>45.0684</v>
+        <v>44.6364</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2241</v>
+        <v>0.2366</v>
       </c>
       <c r="J288" t="n">
-        <v>8.067600000000001</v>
+        <v>8.5176</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.08</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1839</v>
+        <v>0.1974</v>
       </c>
       <c r="J289" t="n">
-        <v>6.6204</v>
+        <v>7.1064</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.87</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1814</v>
+        <v>-0.1916</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.5304</v>
+        <v>-6.8976</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.77</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2831</v>
+        <v>-0.293</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.1916</v>
+        <v>-10.548</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2786</v>
+        <v>1.2599</v>
       </c>
       <c r="J292" t="n">
-        <v>29.4078</v>
+        <v>28.9777</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2314</v>
+        <v>1.2095</v>
       </c>
       <c r="J293" t="n">
-        <v>28.3222</v>
+        <v>27.8185</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.54</v>
       </c>
       <c r="I294" t="n">
-        <v>1.1484</v>
+        <v>1.1202</v>
       </c>
       <c r="J294" t="n">
-        <v>26.4132</v>
+        <v>25.7646</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.37</v>
       </c>
       <c r="I295" t="n">
-        <v>0.9043</v>
+        <v>0.859</v>
       </c>
       <c r="J295" t="n">
-        <v>20.7989</v>
+        <v>19.757</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.97</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2338</v>
+        <v>-0.2079</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.3774</v>
+        <v>-4.7817</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.96</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0228</v>
+        <v>-0.0412</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.5244</v>
+        <v>-0.9476</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0994</v>
+        <v>-0.1201</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.2862</v>
+        <v>-2.7623</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.86</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1452</v>
+        <v>-0.1661</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.3396</v>
+        <v>-3.8203</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.54</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4523</v>
+        <v>-0.4644</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.4029</v>
+        <v>-10.6812</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.46</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5341</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.1141</v>
+        <v>-12.2843</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5147/event_5147_evp_summary.xlsx
+++ b/database/event/5147/event_5147_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.9774</v>
+        <v>7.704</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6333</v>
+        <v>1.5774</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0073</v>
+        <v>2.9038</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9774</v>
+        <v>7.704</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5292</v>
+        <v>3.4479</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4482</v>
+        <v>4.2561</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7501</v>
+        <v>6.5022</v>
       </c>
       <c r="I2" t="n">
-        <v>3.645</v>
+        <v>3.6508</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4482</v>
+        <v>4.2561</v>
       </c>
       <c r="K2" t="n">
         <v>126</v>
@@ -529,7 +529,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0932</v>
+        <v>7.9069</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8157</v>
+        <v>6.6908</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3955</v>
+        <v>1.3699</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4784</v>
+        <v>2.4422</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8157</v>
+        <v>6.6908</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8677</v>
+        <v>2.8536</v>
       </c>
       <c r="G3" t="n">
-        <v>3.948</v>
+        <v>3.8372</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5673</v>
+        <v>4.2711</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4663</v>
+        <v>2.3981</v>
       </c>
       <c r="J3" t="n">
-        <v>3.948</v>
+        <v>3.8372</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4143</v>
+        <v>6.235300000000001</v>
       </c>
       <c r="N3" t="n">
         <v>299</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2278</v>
+        <v>6.22</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2751</v>
+        <v>1.2735</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2108</v>
+        <v>2.2277</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2278</v>
+        <v>6.22</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1026</v>
+        <v>3.0601</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1252</v>
+        <v>3.1599</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3423</v>
+        <v>5.0462</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8848</v>
+        <v>2.8333</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1252</v>
+        <v>3.1599</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -621,7 +621,7 @@
         <v>183</v>
       </c>
       <c r="M4" t="n">
-        <v>6.01</v>
+        <v>5.9932</v>
       </c>
       <c r="N4" t="n">
         <v>299</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2366</v>
+        <v>5.1707</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0722</v>
+        <v>1.0587</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7596</v>
+        <v>1.7497</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2366</v>
+        <v>5.1707</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5215</v>
+        <v>2.5587</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7151</v>
+        <v>2.612</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4252</v>
+        <v>3.1637</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8496</v>
+        <v>1.7763</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7151</v>
+        <v>2.612</v>
       </c>
       <c r="K5" t="n">
         <v>126</v>
@@ -667,7 +667,7 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5647</v>
+        <v>4.3883</v>
       </c>
       <c r="N5" t="n">
         <v>284</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2105</v>
+        <v>4.2113</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8621</v>
+        <v>0.8622</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2925</v>
+        <v>1.3127</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2105</v>
+        <v>4.2113</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6379</v>
+        <v>2.6656</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5726</v>
+        <v>1.5457</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8091</v>
+        <v>3.5653</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0569</v>
+        <v>2.0018</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5726</v>
+        <v>1.5457</v>
       </c>
       <c r="K6" t="n">
         <v>116</v>
@@ -713,7 +713,7 @@
         <v>183</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6295</v>
+        <v>3.5475</v>
       </c>
       <c r="N6" t="n">
         <v>299</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7214</v>
+        <v>3.6531</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7619</v>
+        <v>0.748</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0699</v>
+        <v>1.0584</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7214</v>
+        <v>3.6531</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9615</v>
+        <v>2.9526</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7599</v>
+        <v>0.7005</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8769</v>
+        <v>4.6428</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6335</v>
+        <v>2.6068</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7599</v>
+        <v>0.7005</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>158</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3934</v>
+        <v>3.3073</v>
       </c>
       <c r="N7" t="n">
         <v>284</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6384</v>
+        <v>3.3688</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7449</v>
+        <v>0.6897</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0321</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6384</v>
+        <v>3.3688</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0831</v>
+        <v>1.9125</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5553</v>
+        <v>1.4563</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0831</v>
+        <v>1.9125</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1368</v>
+        <v>1.9636</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5553</v>
+        <v>1.4563</v>
       </c>
       <c r="K8" t="n">
         <v>123</v>
@@ -805,7 +805,7 @@
         <v>106</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6921</v>
+        <v>3.4199</v>
       </c>
       <c r="N8" t="n">
         <v>229</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3569</v>
+        <v>3.3322</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6873</v>
+        <v>0.6823</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9039</v>
+        <v>0.9122</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3569</v>
+        <v>3.3322</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4608</v>
+        <v>2.4789</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8961</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2249</v>
+        <v>2.8643</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7414</v>
+        <v>1.6082</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8961</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>116</v>
@@ -851,7 +851,7 @@
         <v>183</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6375</v>
+        <v>2.4615</v>
       </c>
       <c r="N9" t="n">
         <v>299</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7562</v>
+        <v>2.7519</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5643</v>
+        <v>0.5634</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6478</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7562</v>
+        <v>2.7519</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9826</v>
+        <v>2.0001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7736</v>
+        <v>0.7518</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9826</v>
+        <v>2.0001</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0337</v>
+        <v>2.0535</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7736</v>
+        <v>0.7518</v>
       </c>
       <c r="K10" t="n">
         <v>123</v>
@@ -897,7 +897,7 @@
         <v>106</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8073</v>
+        <v>2.8053</v>
       </c>
       <c r="N10" t="n">
         <v>229</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5909</v>
+        <v>2.4576</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5305</v>
+        <v>0.5032</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5552</v>
+        <v>0.5138</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5909</v>
+        <v>2.4576</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2833</v>
+        <v>1.1781</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3076</v>
+        <v>1.2795</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2833</v>
+        <v>1.1781</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2833</v>
+        <v>1.1781</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3076</v>
+        <v>1.2795</v>
       </c>
       <c r="K11" t="n">
         <v>113</v>
@@ -943,7 +943,7 @@
         <v>133</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5909</v>
+        <v>2.4576</v>
       </c>
       <c r="N11" t="n">
         <v>246</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4329</v>
+        <v>2.3058</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4981</v>
+        <v>0.4721</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4833</v>
+        <v>0.4446</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4329</v>
+        <v>2.3058</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5688</v>
+        <v>2.4857</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1359</v>
+        <v>-0.1799</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8974</v>
+        <v>2.7464</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9721</v>
+        <v>2.8197</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1359</v>
+        <v>-0.1799</v>
       </c>
       <c r="K12" t="n">
         <v>123</v>
@@ -989,7 +989,7 @@
         <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8362</v>
+        <v>2.6398</v>
       </c>
       <c r="N12" t="n">
         <v>229</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3176</v>
+        <v>2.3035</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4745</v>
+        <v>0.4716</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4308</v>
+        <v>0.4436</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3176</v>
+        <v>2.3035</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4426</v>
+        <v>2.2521</v>
       </c>
       <c r="G13" t="n">
-        <v>0.875</v>
+        <v>0.0514</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4426</v>
+        <v>2.2521</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4426</v>
+        <v>1.2645</v>
       </c>
       <c r="J13" t="n">
-        <v>0.875</v>
+        <v>0.0514</v>
       </c>
       <c r="K13" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3176</v>
+        <v>1.3159</v>
       </c>
       <c r="N13" t="n">
-        <v>163</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2905</v>
+        <v>2.2494</v>
       </c>
       <c r="C14" t="n">
-        <v>0.469</v>
+        <v>0.4606</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4185</v>
+        <v>0.4189</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2905</v>
+        <v>2.2494</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2209</v>
+        <v>1.4485</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0696</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4334</v>
+        <v>1.4485</v>
       </c>
       <c r="I14" t="n">
-        <v>1.314</v>
+        <v>1.4485</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0696</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="L14" t="n">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3836</v>
+        <v>2.2494</v>
       </c>
       <c r="N14" t="n">
-        <v>284</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0172</v>
+        <v>1.8983</v>
       </c>
       <c r="C15" t="n">
-        <v>0.413</v>
+        <v>0.3887</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2941</v>
+        <v>0.259</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0172</v>
+        <v>1.8983</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1474</v>
+        <v>1.1156</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8698</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1474</v>
+        <v>1.1156</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1474</v>
+        <v>1.1156</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8698</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>109</v>
@@ -1127,7 +1127,7 @@
         <v>54</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0172</v>
+        <v>1.8984</v>
       </c>
       <c r="N15" t="n">
         <v>163</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0029</v>
+        <v>1.8958</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4101</v>
+        <v>0.3882</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2876</v>
+        <v>0.2578</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0029</v>
+        <v>1.8958</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2733</v>
+        <v>1.1606</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7296</v>
+        <v>0.7352</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2733</v>
+        <v>1.1606</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2733</v>
+        <v>1.1606</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7296</v>
+        <v>0.7352</v>
       </c>
       <c r="K16" t="n">
         <v>113</v>
@@ -1173,7 +1173,7 @@
         <v>133</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0029</v>
+        <v>1.8958</v>
       </c>
       <c r="N16" t="n">
         <v>246</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8888</v>
+        <v>1.812</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3867</v>
+        <v>0.371</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2356</v>
+        <v>0.2197</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8888</v>
+        <v>1.812</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9318</v>
+        <v>0.9493</v>
       </c>
       <c r="G17" t="n">
-        <v>0.957</v>
+        <v>0.8627</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9318</v>
+        <v>0.9493</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9318</v>
+        <v>0.9493</v>
       </c>
       <c r="J17" t="n">
-        <v>0.957</v>
+        <v>0.8627</v>
       </c>
       <c r="K17" t="n">
         <v>105</v>
@@ -1219,7 +1219,7 @@
         <v>56</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8888</v>
+        <v>1.812</v>
       </c>
       <c r="N17" t="n">
         <v>161</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3231</v>
+        <v>1.3072</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2709</v>
+        <v>0.2676</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0219</v>
+        <v>-0.0103</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3231</v>
+        <v>1.3072</v>
       </c>
       <c r="F18" t="n">
-        <v>1.259</v>
+        <v>1.2691</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0641</v>
+        <v>0.0381</v>
       </c>
       <c r="H18" t="n">
-        <v>1.259</v>
+        <v>1.2691</v>
       </c>
       <c r="I18" t="n">
-        <v>1.259</v>
+        <v>1.2691</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0641</v>
+        <v>0.0381</v>
       </c>
       <c r="K18" t="n">
         <v>105</v>
@@ -1265,7 +1265,7 @@
         <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3231</v>
+        <v>1.3072</v>
       </c>
       <c r="N18" t="n">
         <v>161</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1324</v>
+        <v>1.1528</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2319</v>
+        <v>0.236</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1087</v>
+        <v>-0.0806</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1324</v>
+        <v>1.1528</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0213</v>
+        <v>1.4975</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1537</v>
+        <v>-0.3447</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0213</v>
+        <v>1.4975</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0213</v>
+        <v>1.4975</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1537</v>
+        <v>-0.3447</v>
       </c>
       <c r="K19" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L19" t="n">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1324</v>
+        <v>1.1528</v>
       </c>
       <c r="N19" t="n">
-        <v>246</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1044</v>
+        <v>1.088</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2261</v>
+        <v>0.2228</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1215</v>
+        <v>-0.1102</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1044</v>
+        <v>1.088</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4889</v>
+        <v>0.005</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3845</v>
+        <v>1.083</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4889</v>
+        <v>0.005</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4889</v>
+        <v>0.005</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3845</v>
+        <v>1.083</v>
       </c>
       <c r="K20" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1044</v>
+        <v>1.088</v>
       </c>
       <c r="N20" t="n">
-        <v>163</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0541</v>
+        <v>0.9426</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2158</v>
+        <v>0.193</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1444</v>
+        <v>-0.1764</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0541</v>
+        <v>0.9426</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0541</v>
+        <v>0.9426</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0541</v>
+        <v>0.9426</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0541</v>
+        <v>0.9426</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0541</v>
+        <v>0.9426</v>
       </c>
       <c r="N21" t="n">
         <v>106</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6602</v>
+        <v>0.5848</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1352</v>
+        <v>0.1197</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3237</v>
+        <v>-0.3394</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6602</v>
+        <v>0.5848</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6602</v>
+        <v>0.5848</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6602</v>
+        <v>0.5848</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6602</v>
+        <v>0.5848</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6602</v>
+        <v>0.5848</v>
       </c>
       <c r="N22" t="n">
         <v>106</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5766</v>
       </c>
       <c r="C23" t="n">
-        <v>0.112</v>
+        <v>0.1181</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3752</v>
+        <v>-0.3431</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5766</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5766</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5766</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5766</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5766</v>
       </c>
       <c r="N23" t="n">
         <v>102</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.492</v>
+        <v>0.4874</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1007</v>
+        <v>0.0998</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4002</v>
+        <v>-0.3838</v>
       </c>
       <c r="E24" t="n">
-        <v>0.492</v>
+        <v>0.4874</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0536</v>
+        <v>0.1327</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4384</v>
+        <v>0.3547</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0536</v>
+        <v>0.1327</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0536</v>
+        <v>0.1327</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4384</v>
+        <v>0.3547</v>
       </c>
       <c r="K24" t="n">
         <v>105</v>
@@ -1541,7 +1541,7 @@
         <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>0.492</v>
+        <v>0.4874000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>161</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4515</v>
+        <v>0.4768</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0924</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4187</v>
+        <v>-0.3886</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4515</v>
+        <v>0.4768</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1594</v>
+        <v>1.1556</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7079</v>
+        <v>-0.6788</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1594</v>
+        <v>1.1556</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1594</v>
+        <v>1.1556</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7079</v>
+        <v>-0.6788</v>
       </c>
       <c r="K25" t="n">
         <v>105</v>
@@ -1587,7 +1587,7 @@
         <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4515</v>
+        <v>0.4768</v>
       </c>
       <c r="N25" t="n">
         <v>161</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.438</v>
+        <v>0.3516</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0897</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4248</v>
+        <v>-0.4456</v>
       </c>
       <c r="E26" t="n">
-        <v>0.438</v>
+        <v>0.3516</v>
       </c>
       <c r="F26" t="n">
-        <v>0.438</v>
+        <v>0.3516</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.438</v>
+        <v>0.3516</v>
       </c>
       <c r="I26" t="n">
-        <v>0.438</v>
+        <v>0.3516</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.438</v>
+        <v>0.3516</v>
       </c>
       <c r="N26" t="n">
         <v>106</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1716</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0154</v>
+        <v>0.0351</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5899</v>
+        <v>-0.5276</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1716</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.8435</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9972</v>
+        <v>1.0151</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.8435</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4978</v>
+        <v>-0.4736</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9972</v>
+        <v>1.0151</v>
       </c>
       <c r="K27" t="n">
         <v>116</v>
@@ -1679,7 +1679,7 @@
         <v>183</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4994</v>
+        <v>0.5414999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>299</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0531</v>
+        <v>0.0209</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0109</v>
+        <v>0.0043</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6484</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0531</v>
+        <v>0.0209</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6116</v>
+        <v>1.6319</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.6647</v>
+        <v>-1.611</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6116</v>
+        <v>1.6319</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6116</v>
+        <v>1.6319</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.6647</v>
+        <v>-1.611</v>
       </c>
       <c r="K28" t="n">
         <v>113</v>
@@ -1725,7 +1725,7 @@
         <v>133</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.05310000000000015</v>
+        <v>0.02089999999999992</v>
       </c>
       <c r="N28" t="n">
         <v>246</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5072</v>
+        <v>-0.3788</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1038</v>
+        <v>-0.0776</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8551</v>
+        <v>-0.7783</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5072</v>
+        <v>-0.3788</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5404</v>
+        <v>0.5789</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.0476</v>
+        <v>-0.9577</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5404</v>
+        <v>0.5789</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5543</v>
+        <v>0.5944</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.0476</v>
+        <v>-0.9577</v>
       </c>
       <c r="K29" t="n">
         <v>123</v>
@@ -1771,7 +1771,7 @@
         <v>106</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4933000000000001</v>
+        <v>-0.3633</v>
       </c>
       <c r="N29" t="n">
         <v>229</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6135</v>
+        <v>-0.6062</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1256</v>
+        <v>-0.1241</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9035</v>
+        <v>-0.8819</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6135</v>
+        <v>-0.6062</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6135</v>
+        <v>-0.6062</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6135</v>
+        <v>-0.6062</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6135</v>
+        <v>-0.6062</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6135</v>
+        <v>-0.6062</v>
       </c>
       <c r="N30" t="n">
         <v>102</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.669</v>
+        <v>-0.6088</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.137</v>
+        <v>-0.1246</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9287</v>
+        <v>-0.8831</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.669</v>
+        <v>-0.6088</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.669</v>
+        <v>-0.6088</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.669</v>
+        <v>-0.6088</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.669</v>
+        <v>-0.6088</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.669</v>
+        <v>-0.6088</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8588</v>
+        <v>-0.8035</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1758</v>
+        <v>-0.1645</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.0151</v>
+        <v>-0.9718</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8588</v>
+        <v>-0.8035</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5605</v>
+        <v>-0.5061</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2983</v>
+        <v>-0.2974</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5605</v>
+        <v>-0.5061</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5605</v>
+        <v>-0.5061</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2983</v>
+        <v>-0.2974</v>
       </c>
       <c r="K32" t="n">
         <v>105</v>
@@ -1909,7 +1909,7 @@
         <v>56</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8588</v>
+        <v>-0.8035</v>
       </c>
       <c r="N32" t="n">
         <v>161</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8822</v>
+        <v>-0.8597</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1806</v>
+        <v>-0.176</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0258</v>
+        <v>-0.9974</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8822</v>
+        <v>-0.8597</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8822</v>
+        <v>-0.8597</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8822</v>
+        <v>-0.8597</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8822</v>
+        <v>-0.8597</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8822</v>
+        <v>-0.8597</v>
       </c>
       <c r="N33" t="n">
         <v>102</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9702</v>
+        <v>-0.8932</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1986</v>
+        <v>-0.1829</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0659</v>
+        <v>-1.0127</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9702</v>
+        <v>-0.8932</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9702</v>
+        <v>-0.8932</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9702</v>
+        <v>-0.8932</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9702</v>
+        <v>-0.8932</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9702</v>
+        <v>-0.8932</v>
       </c>
       <c r="N34" t="n">
         <v>106</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0515</v>
+        <v>-0.9677</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2153</v>
+        <v>-0.1981</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1029</v>
+        <v>-1.0466</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0515</v>
+        <v>-0.9677</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0515</v>
+        <v>0.3238</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-1.2915</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0515</v>
+        <v>0.3238</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0515</v>
+        <v>0.3325</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-1.2915</v>
       </c>
       <c r="K35" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0515</v>
+        <v>-0.9590000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>102</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1134</v>
+        <v>-1.0698</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.228</v>
+        <v>-0.219</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.131</v>
+        <v>-1.0931</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1134</v>
+        <v>-1.0698</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2718</v>
+        <v>-1.0698</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.3852</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2718</v>
+        <v>-1.0698</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2788</v>
+        <v>-1.0698</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.3852</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="L36" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1064</v>
+        <v>-1.0698</v>
       </c>
       <c r="N36" t="n">
-        <v>229</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1623</v>
+        <v>-1.1891</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.238</v>
+        <v>-0.2435</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1533</v>
+        <v>-1.1475</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1623</v>
+        <v>-1.1891</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5462</v>
+        <v>-0.6056</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6161</v>
+        <v>-0.5835</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5462</v>
+        <v>-0.6056</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5462</v>
+        <v>-0.6056</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6161</v>
+        <v>-0.5835</v>
       </c>
       <c r="K37" t="n">
         <v>109</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1623</v>
+        <v>-1.1891</v>
       </c>
       <c r="N37" t="n">
         <v>163</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2424</v>
+        <v>-1.2017</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2544</v>
+        <v>-0.246</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1898</v>
+        <v>-1.1532</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2424</v>
+        <v>-1.2017</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2424</v>
+        <v>-1.2017</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2424</v>
+        <v>-1.2017</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2424</v>
+        <v>-1.2017</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2424</v>
+        <v>-1.2017</v>
       </c>
       <c r="N38" t="n">
         <v>106</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5221</v>
+        <v>-1.4839</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3116</v>
+        <v>-0.3038</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3171</v>
+        <v>-1.2818</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5221</v>
+        <v>-1.4839</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9458</v>
+        <v>-0.9363</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5763</v>
+        <v>-0.5476</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9458</v>
+        <v>-0.9363</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9458</v>
+        <v>-0.9363</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5763</v>
+        <v>-0.5476</v>
       </c>
       <c r="K39" t="n">
         <v>109</v>
@@ -2231,7 +2231,7 @@
         <v>54</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5221</v>
+        <v>-1.4839</v>
       </c>
       <c r="N39" t="n">
         <v>163</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.567</v>
+        <v>-2.4846</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5256</v>
+        <v>-0.5087</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7928</v>
+        <v>-1.7376</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.567</v>
+        <v>-2.4846</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4988</v>
+        <v>-1.4225</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.0682</v>
+        <v>-1.0621</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4988</v>
+        <v>-1.4225</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4988</v>
+        <v>-1.4225</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.0682</v>
+        <v>-1.0621</v>
       </c>
       <c r="K40" t="n">
         <v>113</v>
@@ -2277,7 +2277,7 @@
         <v>133</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.567</v>
+        <v>-2.4846</v>
       </c>
       <c r="N40" t="n">
         <v>246</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0511</v>
+        <v>-2.7909</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6247</v>
+        <v>-0.5714</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0131</v>
+        <v>-1.8772</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0511</v>
+        <v>-2.7909</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.8873</v>
+        <v>-2.6331</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1638</v>
+        <v>-0.1578</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.8873</v>
+        <v>-2.6331</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5591</v>
+        <v>-1.4784</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1638</v>
+        <v>-0.1578</v>
       </c>
       <c r="K41" t="n">
         <v>126</v>
@@ -2323,7 +2323,7 @@
         <v>158</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7229</v>
+        <v>-1.6362</v>
       </c>
       <c r="N41" t="n">
         <v>284</v>
@@ -2429,10 +2429,10 @@
         <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1.11</v>
+        <v>1.1168</v>
       </c>
       <c r="J2" t="n">
-        <v>33.3</v>
+        <v>33.504</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5235</v>
+        <v>0.4829</v>
       </c>
       <c r="J3" t="n">
-        <v>15.705</v>
+        <v>14.487</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1915</v>
+        <v>0.1608</v>
       </c>
       <c r="J4" t="n">
-        <v>5.745</v>
+        <v>4.824</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4323</v>
+        <v>-0.3893</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.969</v>
+        <v>-11.679</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.76</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6911</v>
+        <v>-0.6584</v>
       </c>
       <c r="J6" t="n">
-        <v>-20.733</v>
+        <v>-19.752</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.72</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1781</v>
+        <v>1.1565</v>
       </c>
       <c r="J7" t="n">
-        <v>35.343</v>
+        <v>34.695</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0633</v>
+        <v>-0.0496</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.899</v>
+        <v>-1.488</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.97</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0633</v>
+        <v>-0.0496</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.899</v>
+        <v>-1.488</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1045</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.135</v>
+        <v>-2.607</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.74</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3163</v>
+        <v>-0.2998</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.489000000000001</v>
+        <v>-8.994</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9083</v>
+        <v>0.8923</v>
       </c>
       <c r="J12" t="n">
-        <v>21.7992</v>
+        <v>21.4152</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.36</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8694</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>20.8656</v>
+        <v>20.4072</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.25</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6484</v>
+        <v>0.6173</v>
       </c>
       <c r="J14" t="n">
-        <v>15.5616</v>
+        <v>14.8152</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4778</v>
+        <v>0.4438</v>
       </c>
       <c r="J15" t="n">
-        <v>11.4672</v>
+        <v>10.6512</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3556</v>
+        <v>-0.3151</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.5344</v>
+        <v>-7.5624</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8756</v>
+        <v>0.8366</v>
       </c>
       <c r="J17" t="n">
-        <v>21.0144</v>
+        <v>20.0784</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2515</v>
+        <v>0.205</v>
       </c>
       <c r="J18" t="n">
-        <v>6.036</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.88</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1618</v>
+        <v>-0.1429</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.8832</v>
+        <v>-3.4296</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3578</v>
+        <v>-0.3432</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.587199999999999</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.45</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5584</v>
+        <v>-0.5675</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.4016</v>
+        <v>-13.62</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>0.076</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>2.052</v>
+        <v>1.6956</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0516</v>
+        <v>0.0412</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3932</v>
+        <v>1.1124</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1697</v>
+        <v>-0.1516</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.5819</v>
+        <v>-4.0932</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.84</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2004</v>
+        <v>-0.1813</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.4108</v>
+        <v>-4.8951</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.62</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4078</v>
+        <v>-0.3973</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.0106</v>
+        <v>-10.7271</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8433</v>
+        <v>0.7745</v>
       </c>
       <c r="J27" t="n">
-        <v>22.7691</v>
+        <v>20.9115</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4246</v>
+        <v>0.3609</v>
       </c>
       <c r="J28" t="n">
-        <v>11.4642</v>
+        <v>9.744300000000001</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2634</v>
+        <v>0.2149</v>
       </c>
       <c r="J29" t="n">
-        <v>7.1118</v>
+        <v>5.8023</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0375</v>
+        <v>0.0252</v>
       </c>
       <c r="J30" t="n">
-        <v>1.0125</v>
+        <v>0.6804</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.76</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3071</v>
+        <v>-0.2915</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.291700000000001</v>
+        <v>-7.8705</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0904</v>
+        <v>1.092</v>
       </c>
       <c r="J32" t="n">
-        <v>27.26</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.23</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6121</v>
+        <v>0.578</v>
       </c>
       <c r="J33" t="n">
-        <v>15.3025</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.11</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3397</v>
+        <v>0.3056</v>
       </c>
       <c r="J34" t="n">
-        <v>8.4925</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.07</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2327</v>
+        <v>0.2025</v>
       </c>
       <c r="J35" t="n">
-        <v>5.8175</v>
+        <v>5.0625</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0293</v>
+        <v>-0.0238</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7325</v>
+        <v>-0.595</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3729</v>
+        <v>0.3179</v>
       </c>
       <c r="J37" t="n">
-        <v>9.3225</v>
+        <v>7.9475</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1305</v>
+        <v>0.0984</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2625</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.95</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0834</v>
+        <v>-0.0687</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.085</v>
+        <v>-1.7175</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.84</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2084</v>
+        <v>-0.188</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.21</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2289</v>
+        <v>-0.2085</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.7225</v>
+        <v>-5.2125</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8753</v>
+        <v>0.8609</v>
       </c>
       <c r="J42" t="n">
-        <v>20.1319</v>
+        <v>19.8007</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7919</v>
+        <v>0.7778</v>
       </c>
       <c r="J43" t="n">
-        <v>18.2137</v>
+        <v>17.8894</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.32</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6804</v>
       </c>
       <c r="J44" t="n">
-        <v>15.916</v>
+        <v>15.6492</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.17</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4614</v>
+        <v>0.4378</v>
       </c>
       <c r="J45" t="n">
-        <v>10.6122</v>
+        <v>10.0694</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.01</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0146</v>
+        <v>0.0044</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3358</v>
+        <v>0.1012</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.15</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3985</v>
+        <v>0.3488</v>
       </c>
       <c r="J47" t="n">
-        <v>9.1655</v>
+        <v>8.022399999999999</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.91</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1205</v>
+        <v>-0.1056</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.7715</v>
+        <v>-2.4288</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1971</v>
+        <v>-0.1796</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.5333</v>
+        <v>-4.1308</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3575</v>
+        <v>-0.3428</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.2225</v>
+        <v>-7.8844</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.54</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4731</v>
+        <v>-0.4691</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.8813</v>
+        <v>-10.7893</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.64</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1206</v>
+        <v>1.1128</v>
       </c>
       <c r="J52" t="n">
-        <v>32.4974</v>
+        <v>32.2712</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.46</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8829</v>
+        <v>0.8693</v>
       </c>
       <c r="J53" t="n">
-        <v>25.6041</v>
+        <v>25.2097</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6014</v>
+        <v>0.5952</v>
       </c>
       <c r="J54" t="n">
-        <v>17.4406</v>
+        <v>17.2608</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4567</v>
+        <v>0.4326</v>
       </c>
       <c r="J55" t="n">
-        <v>13.2443</v>
+        <v>12.5454</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.01</v>
       </c>
       <c r="I56" t="n">
-        <v>0.008</v>
+        <v>-0.0027</v>
       </c>
       <c r="J56" t="n">
-        <v>0.232</v>
+        <v>-0.07829999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0285</v>
+        <v>-0.0182</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.8265</v>
+        <v>-0.5278</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.77</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2593</v>
+        <v>-0.2432</v>
       </c>
       <c r="J58" t="n">
-        <v>-7.5197</v>
+        <v>-7.0528</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2954</v>
+        <v>-0.2794</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.566599999999999</v>
+        <v>-8.102600000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3409</v>
+        <v>-0.3261</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.886100000000001</v>
+        <v>-9.456899999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.386</v>
+        <v>-0.3736</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.194</v>
+        <v>-10.8344</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.07</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1655</v>
+        <v>0.1484</v>
       </c>
       <c r="J62" t="n">
-        <v>4.7995</v>
+        <v>4.3036</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0459</v>
+        <v>0.0354</v>
       </c>
       <c r="J63" t="n">
-        <v>1.3311</v>
+        <v>1.0266</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0796</v>
+        <v>-0.0665</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.3084</v>
+        <v>-1.9285</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.87</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1719</v>
+        <v>-0.1528</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.9851</v>
+        <v>-4.4312</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.411</v>
+        <v>-0.401</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.919</v>
+        <v>-11.629</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.72</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7408</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>21.4832</v>
+        <v>20.1289</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.25</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3588</v>
+        <v>0.2999</v>
       </c>
       <c r="J68" t="n">
-        <v>10.4052</v>
+        <v>8.697100000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0951</v>
+        <v>0.0708</v>
       </c>
       <c r="J69" t="n">
-        <v>2.7579</v>
+        <v>2.0532</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0392</v>
+        <v>0.0266</v>
       </c>
       <c r="J70" t="n">
-        <v>1.1368</v>
+        <v>0.7714</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2163</v>
+        <v>-0.1967</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.2727</v>
+        <v>-5.7043</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.68</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1501</v>
+        <v>1.1446</v>
       </c>
       <c r="J72" t="n">
-        <v>23.002</v>
+        <v>22.892</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.47</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8821</v>
+        <v>0.8721</v>
       </c>
       <c r="J73" t="n">
-        <v>17.642</v>
+        <v>17.442</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.38</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7633</v>
+        <v>0.7551</v>
       </c>
       <c r="J74" t="n">
-        <v>15.266</v>
+        <v>15.102</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.34</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7073</v>
+        <v>0.7005</v>
       </c>
       <c r="J75" t="n">
-        <v>14.146</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.27</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6007</v>
       </c>
       <c r="J76" t="n">
-        <v>12.086</v>
+        <v>12.014</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.84</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.182</v>
+        <v>-0.1664</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.64</v>
+        <v>-3.328</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1927</v>
+        <v>-0.1773</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.854</v>
+        <v>-3.546</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2241</v>
+        <v>-0.209</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.482</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2637</v>
+        <v>-0.2492</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.274</v>
+        <v>-4.984</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.32</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6508</v>
+        <v>-0.673</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.016</v>
+        <v>-13.46</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.58</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0572</v>
+        <v>1.0467</v>
       </c>
       <c r="J82" t="n">
-        <v>29.6016</v>
+        <v>29.3076</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.53</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9902</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>27.7256</v>
+        <v>27.3644</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.24</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5767</v>
+        <v>0.5694</v>
       </c>
       <c r="J84" t="n">
-        <v>16.1476</v>
+        <v>15.9432</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>0.02</v>
+        <v>0.0101</v>
       </c>
       <c r="J85" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2828</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5849</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.3772</v>
+        <v>-15.3972</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.97</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0437</v>
+        <v>-0.0345</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.2236</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.92</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.111</v>
+        <v>-0.0964</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.108</v>
+        <v>-2.6992</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2277</v>
+        <v>-0.2091</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.3756</v>
+        <v>-5.8548</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.77</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2664</v>
+        <v>-0.2479</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.4592</v>
+        <v>-6.9412</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.74</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2949</v>
+        <v>-0.277</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.257199999999999</v>
+        <v>-7.756</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.24</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5143</v>
+        <v>0.4864</v>
       </c>
       <c r="J92" t="n">
-        <v>12.8575</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1502</v>
+        <v>0.116</v>
       </c>
       <c r="J93" t="n">
-        <v>3.755</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.84</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2004</v>
+        <v>-0.1813</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.01</v>
+        <v>-4.5325</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.64</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.39</v>
+        <v>-0.3778</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.75</v>
+        <v>-9.445</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4256</v>
+        <v>-0.4168</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.64</v>
+        <v>-10.42</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.43</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8754</v>
+        <v>0.8601</v>
       </c>
       <c r="J97" t="n">
-        <v>21.885</v>
+        <v>21.5025</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.38</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>20.0725</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1821</v>
+        <v>0.1543</v>
       </c>
       <c r="J99" t="n">
-        <v>4.5525</v>
+        <v>3.8575</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0801</v>
+        <v>-0.0595</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.0025</v>
+        <v>-1.4875</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.658</v>
+        <v>-0.6243</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.45</v>
+        <v>-15.6075</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7248</v>
+        <v>0.6905</v>
       </c>
       <c r="J102" t="n">
-        <v>21.0192</v>
+        <v>20.0245</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.16</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3555</v>
+        <v>0.3018</v>
       </c>
       <c r="J103" t="n">
-        <v>10.3095</v>
+        <v>8.7522</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1507</v>
+        <v>-0.1308</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.3703</v>
+        <v>-3.7932</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1841</v>
+        <v>-0.1634</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.3389</v>
+        <v>-4.7386</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2261</v>
+        <v>-0.2057</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.5569</v>
+        <v>-5.9653</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4505</v>
+        <v>0.4143</v>
       </c>
       <c r="J107" t="n">
-        <v>13.0645</v>
+        <v>12.0147</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.12</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3824</v>
+        <v>0.3412</v>
       </c>
       <c r="J108" t="n">
-        <v>11.0896</v>
+        <v>9.8948</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.278</v>
+        <v>0.2405</v>
       </c>
       <c r="J109" t="n">
-        <v>8.061999999999999</v>
+        <v>6.9745</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1441</v>
+        <v>-0.114</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.1789</v>
+        <v>-3.306</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2691</v>
+        <v>-0.2293</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.8039</v>
+        <v>-6.6497</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.22</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4706</v>
+        <v>0.4243</v>
       </c>
       <c r="J112" t="n">
-        <v>13.1768</v>
+        <v>11.8804</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2434</v>
+        <v>0.1973</v>
       </c>
       <c r="J113" t="n">
-        <v>6.8152</v>
+        <v>5.5244</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1083</v>
+        <v>0.0798</v>
       </c>
       <c r="J114" t="n">
-        <v>3.0324</v>
+        <v>2.2344</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.7</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3427</v>
+        <v>-0.3272</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.595599999999999</v>
+        <v>-9.1616</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3519</v>
+        <v>-0.3371</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.853199999999999</v>
+        <v>-9.438800000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.44</v>
       </c>
       <c r="I117" t="n">
-        <v>0.886</v>
+        <v>0.8707</v>
       </c>
       <c r="J117" t="n">
-        <v>24.808</v>
+        <v>24.3796</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.3</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6803</v>
+        <v>0.6657</v>
       </c>
       <c r="J118" t="n">
-        <v>19.0484</v>
+        <v>18.6396</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.16</v>
       </c>
       <c r="I119" t="n">
-        <v>0.456</v>
+        <v>0.4253</v>
       </c>
       <c r="J119" t="n">
-        <v>12.768</v>
+        <v>11.9084</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0611</v>
       </c>
       <c r="J120" t="n">
-        <v>2.1784</v>
+        <v>1.7108</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6382</v>
+        <v>-0.6037</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.8696</v>
+        <v>-16.9036</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4864</v>
+        <v>0.4444</v>
       </c>
       <c r="J122" t="n">
-        <v>13.6192</v>
+        <v>12.4432</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3301</v>
+        <v>0.2774</v>
       </c>
       <c r="J123" t="n">
-        <v>9.242800000000001</v>
+        <v>7.7672</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0444</v>
+        <v>0.0298</v>
       </c>
       <c r="J124" t="n">
-        <v>1.2432</v>
+        <v>0.8344</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.87</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1793</v>
+        <v>-0.1589</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.0204</v>
+        <v>-4.4492</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.356</v>
+        <v>-0.3417</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.968</v>
+        <v>-9.567600000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.38</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8303</v>
+        <v>0.8161</v>
       </c>
       <c r="J127" t="n">
-        <v>23.2484</v>
+        <v>22.8508</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5815</v>
       </c>
       <c r="J128" t="n">
-        <v>16.6404</v>
+        <v>16.282</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.95</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2039</v>
+        <v>-0.1686</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.7092</v>
+        <v>-4.7208</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.87</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4234</v>
+        <v>-0.3804</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.8552</v>
+        <v>-10.6512</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8767</v>
+        <v>-0.8592</v>
       </c>
       <c r="J131" t="n">
-        <v>-24.5476</v>
+        <v>-24.0576</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.93</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0876</v>
+        <v>-0.074</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.0148</v>
+        <v>-1.702</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.8</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.232</v>
+        <v>-0.2156</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.336</v>
+        <v>-4.9588</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.75</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2783</v>
+        <v>-0.2618</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.4009</v>
+        <v>-6.0214</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.7</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3242</v>
+        <v>-0.3085</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.4566</v>
+        <v>-7.0955</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3516</v>
+        <v>-0.337</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.0868</v>
+        <v>-7.751</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.83</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5057</v>
+        <v>1.5386</v>
       </c>
       <c r="J137" t="n">
-        <v>34.6311</v>
+        <v>35.3878</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.71</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3557</v>
+        <v>1.378</v>
       </c>
       <c r="J138" t="n">
-        <v>31.1811</v>
+        <v>31.694</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4854</v>
+        <v>0.4547</v>
       </c>
       <c r="J139" t="n">
-        <v>11.1642</v>
+        <v>10.4581</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.02</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0481</v>
+        <v>0.0311</v>
       </c>
       <c r="J140" t="n">
-        <v>1.1063</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.55</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.65</v>
+        <v>-11.8588</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.01</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1072</v>
+        <v>0.0905</v>
       </c>
       <c r="J142" t="n">
-        <v>2.144</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.78</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2486</v>
+        <v>-0.2329</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.972</v>
+        <v>-4.658</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.67</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3486</v>
+        <v>-0.3343</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.972</v>
+        <v>-6.686</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3666</v>
+        <v>-0.3532</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.332</v>
+        <v>-7.064</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4024</v>
+        <v>-0.3912</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.048</v>
+        <v>-7.824</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3758</v>
+        <v>1.3993</v>
       </c>
       <c r="J147" t="n">
-        <v>27.516</v>
+        <v>27.986</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.47</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0292</v>
+        <v>1.0368</v>
       </c>
       <c r="J148" t="n">
-        <v>20.584</v>
+        <v>20.736</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.37</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8617</v>
+        <v>0.851</v>
       </c>
       <c r="J149" t="n">
-        <v>17.234</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.27</v>
       </c>
       <c r="I150" t="n">
-        <v>0.6661</v>
+        <v>0.644</v>
       </c>
       <c r="J150" t="n">
-        <v>13.322</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.17</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4491</v>
+        <v>0.4185</v>
       </c>
       <c r="J151" t="n">
-        <v>8.981999999999999</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.653</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>18.937</v>
+        <v>17.2927</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1093</v>
+        <v>-0.0921</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.1697</v>
+        <v>-2.6709</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.92</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1213</v>
+        <v>-0.1033</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.5177</v>
+        <v>-2.9957</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1558</v>
+        <v>-0.1361</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.5182</v>
+        <v>-3.9469</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2597</v>
+        <v>-0.24</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.5313</v>
+        <v>-6.96</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6311</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>18.3019</v>
+        <v>17.2347</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.519</v>
+        <v>0.4789</v>
       </c>
       <c r="J158" t="n">
-        <v>15.051</v>
+        <v>13.8881</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2741</v>
+        <v>0.2385</v>
       </c>
       <c r="J159" t="n">
-        <v>7.9489</v>
+        <v>6.9165</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2185</v>
+        <v>0.1865</v>
       </c>
       <c r="J160" t="n">
-        <v>6.3365</v>
+        <v>5.4085</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4363</v>
+        <v>-0.3935</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.6527</v>
+        <v>-11.4115</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6113</v>
+        <v>0.5542</v>
       </c>
       <c r="J162" t="n">
-        <v>14.0599</v>
+        <v>12.7466</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2617</v>
+        <v>0.214</v>
       </c>
       <c r="J163" t="n">
-        <v>6.0191</v>
+        <v>4.922</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.89</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1543</v>
+        <v>-0.1349</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.5489</v>
+        <v>-3.1027</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.86</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1868</v>
+        <v>-0.1665</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.2964</v>
+        <v>-3.8295</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.62</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4157</v>
+        <v>-0.4066</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.5611</v>
+        <v>-9.351800000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.83</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5319</v>
+        <v>1.5702</v>
       </c>
       <c r="J167" t="n">
-        <v>35.2337</v>
+        <v>36.1146</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.17</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4769</v>
+        <v>0.4432</v>
       </c>
       <c r="J168" t="n">
-        <v>10.9687</v>
+        <v>10.1936</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4307</v>
+        <v>0.3968</v>
       </c>
       <c r="J169" t="n">
-        <v>9.9061</v>
+        <v>9.1264</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1384</v>
+        <v>-0.1114</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.1832</v>
+        <v>-2.5622</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.175</v>
+        <v>-0.1439</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.025</v>
+        <v>-3.3097</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1649</v>
+        <v>0.131</v>
       </c>
       <c r="J172" t="n">
-        <v>3.6278</v>
+        <v>2.882</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.139</v>
+        <v>0.1087</v>
       </c>
       <c r="J173" t="n">
-        <v>3.058</v>
+        <v>2.3914</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.71</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3207</v>
+        <v>-0.3041</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.0554</v>
+        <v>-6.6902</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3483</v>
+        <v>-0.3331</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.6626</v>
+        <v>-7.3282</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.65</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3756</v>
+        <v>-0.3622</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.263199999999999</v>
+        <v>-7.9684</v>
       </c>
     </row>
     <row r="177">
@@ -9469,10 +9469,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7735</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>17.017</v>
+        <v>16.445</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.31</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7735</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>17.017</v>
+        <v>16.445</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3615</v>
+        <v>0.3275</v>
       </c>
       <c r="J180" t="n">
-        <v>7.953</v>
+        <v>7.205</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.602</v>
+        <v>-0.5667</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.244</v>
+        <v>-12.4674</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4474</v>
+        <v>0.3923</v>
       </c>
       <c r="J182" t="n">
-        <v>10.7376</v>
+        <v>9.4152</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.99</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.016</v>
+        <v>-0.0114</v>
       </c>
       <c r="J183" t="n">
-        <v>-0.384</v>
+        <v>-0.2736</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1389</v>
+        <v>-0.1217</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.3336</v>
+        <v>-2.9208</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2321</v>
+        <v>-0.2124</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.5704</v>
+        <v>-5.0976</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4625</v>
+        <v>-0.4579</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.1</v>
+        <v>-10.9896</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.01</v>
       </c>
       <c r="I187" t="n">
-        <v>1.7199</v>
+        <v>1.7733</v>
       </c>
       <c r="J187" t="n">
-        <v>41.2776</v>
+        <v>42.5592</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9418</v>
+        <v>0.9341</v>
       </c>
       <c r="J188" t="n">
-        <v>22.6032</v>
+        <v>22.4184</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3401</v>
+        <v>0.3081</v>
       </c>
       <c r="J189" t="n">
-        <v>8.1624</v>
+        <v>7.3944</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.11</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3147</v>
+        <v>0.2829</v>
       </c>
       <c r="J190" t="n">
-        <v>7.5528</v>
+        <v>6.7896</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0042</v>
+        <v>-0.007</v>
       </c>
       <c r="J191" t="n">
-        <v>0.1008</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.307</v>
+        <v>0.2582</v>
       </c>
       <c r="J192" t="n">
-        <v>7.675</v>
+        <v>6.455</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1008</v>
+        <v>-0.0866</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.52</v>
+        <v>-2.165</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1131</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.8275</v>
+        <v>-2.4525</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1585</v>
+        <v>-0.1412</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.9625</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.46</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5456</v>
+        <v>-0.552</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.64</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.6</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2245</v>
+        <v>1.2403</v>
       </c>
       <c r="J197" t="n">
-        <v>30.6125</v>
+        <v>31.0075</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.25</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6432</v>
+        <v>0.6148</v>
       </c>
       <c r="J198" t="n">
-        <v>16.08</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5592</v>
+        <v>0.5286</v>
       </c>
       <c r="J199" t="n">
-        <v>13.98</v>
+        <v>13.215</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.17</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4702</v>
+        <v>0.4381</v>
       </c>
       <c r="J200" t="n">
-        <v>11.755</v>
+        <v>10.9525</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.1</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2995</v>
+        <v>0.2678</v>
       </c>
       <c r="J201" t="n">
-        <v>7.4875</v>
+        <v>6.695</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.2</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4333</v>
+        <v>0.3757</v>
       </c>
       <c r="J202" t="n">
-        <v>12.999</v>
+        <v>11.271</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.05</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1476</v>
+        <v>0.1137</v>
       </c>
       <c r="J203" t="n">
-        <v>4.428</v>
+        <v>3.411</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1117</v>
+        <v>-0.0939</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.351</v>
+        <v>-2.817</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1238</v>
+        <v>-0.1052</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.714</v>
+        <v>-3.156</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1356</v>
+        <v>-0.1164</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.068</v>
+        <v>-3.492</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5778</v>
+        <v>0.5381</v>
       </c>
       <c r="J207" t="n">
-        <v>17.334</v>
+        <v>16.143</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.12</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3862</v>
+        <v>0.3443</v>
       </c>
       <c r="J208" t="n">
-        <v>11.586</v>
+        <v>10.329</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.04</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1639</v>
+        <v>0.1343</v>
       </c>
       <c r="J209" t="n">
-        <v>4.917</v>
+        <v>4.029</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.98</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1045</v>
+        <v>-0.0799</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.135</v>
+        <v>-2.397</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.82</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5475</v>
+        <v>-0.5067</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.425</v>
+        <v>-15.201</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.47</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0531</v>
+        <v>1.0594</v>
       </c>
       <c r="J212" t="n">
-        <v>24.2213</v>
+        <v>24.3662</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.41</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9569</v>
+        <v>0.9478</v>
       </c>
       <c r="J213" t="n">
-        <v>22.0087</v>
+        <v>21.7994</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.25</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>14.8281</v>
+        <v>14.1542</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.1</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3027</v>
+        <v>0.2708</v>
       </c>
       <c r="J215" t="n">
-        <v>6.9621</v>
+        <v>6.2284</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.0415</v>
+        <v>-0.0362</v>
       </c>
       <c r="J216" t="n">
-        <v>-0.9545</v>
+        <v>-0.8326</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.12</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3288</v>
+        <v>0.2792</v>
       </c>
       <c r="J217" t="n">
-        <v>7.5624</v>
+        <v>6.4216</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.99</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0112</v>
+        <v>-0.0069</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.2576</v>
+        <v>-0.1587</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0454</v>
+        <v>-0.0361</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.0442</v>
+        <v>-0.8303</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.71</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3242</v>
+        <v>-0.3075</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.4566</v>
+        <v>-7.0725</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.528</v>
+        <v>-0.5317</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.144</v>
+        <v>-12.2291</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.01</v>
       </c>
       <c r="I222" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0575</v>
       </c>
       <c r="J222" t="n">
-        <v>1.8536</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.9</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1301</v>
+        <v>-0.115</v>
       </c>
       <c r="J223" t="n">
-        <v>-3.6428</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.8</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2346</v>
+        <v>-0.217</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.5688</v>
+        <v>-6.076</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.74</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2911</v>
+        <v>-0.2738</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.1508</v>
+        <v>-7.6664</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.58</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4363</v>
+        <v>-0.4281</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.2164</v>
+        <v>-11.9868</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.84</v>
       </c>
       <c r="I227" t="n">
-        <v>0.956</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J227" t="n">
-        <v>26.768</v>
+        <v>25.0516</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1986</v>
+        <v>0.1583</v>
       </c>
       <c r="J228" t="n">
-        <v>5.5608</v>
+        <v>4.4324</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.05</v>
       </c>
       <c r="I229" t="n">
-        <v>0.0935</v>
+        <v>0.0696</v>
       </c>
       <c r="J229" t="n">
-        <v>2.618</v>
+        <v>1.9488</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0377</v>
+        <v>0.0253</v>
       </c>
       <c r="J230" t="n">
-        <v>1.0556</v>
+        <v>0.7084</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1146</v>
+        <v>-0.0969</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.2088</v>
+        <v>-2.7132</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.39</v>
       </c>
       <c r="I232" t="n">
-        <v>0.979</v>
+        <v>0.9742</v>
       </c>
       <c r="J232" t="n">
-        <v>28.391</v>
+        <v>28.2518</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1637</v>
+        <v>0.1342</v>
       </c>
       <c r="J233" t="n">
-        <v>4.7473</v>
+        <v>3.8918</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0044</v>
+        <v>-0.0024</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.1276</v>
+        <v>-0.0696</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1049</v>
+        <v>-0.0801</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.0421</v>
+        <v>-2.3229</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6852</v>
+        <v>-0.6515</v>
       </c>
       <c r="J236" t="n">
-        <v>-19.8708</v>
+        <v>-18.8935</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.19</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4229</v>
+        <v>0.3658</v>
       </c>
       <c r="J237" t="n">
-        <v>12.2641</v>
+        <v>10.6082</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2575</v>
+        <v>0.2102</v>
       </c>
       <c r="J238" t="n">
-        <v>7.4675</v>
+        <v>6.0958</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.97</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0567</v>
+        <v>-0.0448</v>
       </c>
       <c r="J239" t="n">
-        <v>-1.6443</v>
+        <v>-1.2992</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0842</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.4418</v>
+        <v>-2.0039</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3818</v>
+        <v>-0.3696</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.0722</v>
+        <v>-10.7184</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8869</v>
+        <v>0.8677</v>
       </c>
       <c r="J242" t="n">
-        <v>30.1546</v>
+        <v>29.5018</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.25</v>
       </c>
       <c r="I243" t="n">
-        <v>0.661</v>
+        <v>0.6271</v>
       </c>
       <c r="J243" t="n">
-        <v>22.474</v>
+        <v>21.3214</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.24</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6397</v>
+        <v>0.605</v>
       </c>
       <c r="J244" t="n">
-        <v>21.7498</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1143</v>
+        <v>0.0931</v>
       </c>
       <c r="J245" t="n">
-        <v>3.8862</v>
+        <v>3.1654</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.83</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5451</v>
+        <v>-0.5059</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.5334</v>
+        <v>-17.2006</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6466</v>
+        <v>0.591</v>
       </c>
       <c r="J247" t="n">
-        <v>21.9844</v>
+        <v>20.094</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.93</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1073</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.6482</v>
+        <v>-3.0906</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1073</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.6482</v>
+        <v>-3.0906</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1644</v>
+        <v>-0.1448</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.5896</v>
+        <v>-4.9232</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.379</v>
+        <v>-0.3663</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.886</v>
+        <v>-12.4542</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.52</v>
       </c>
       <c r="I252" t="n">
-        <v>1.116</v>
+        <v>1.1283</v>
       </c>
       <c r="J252" t="n">
-        <v>30.132</v>
+        <v>30.4641</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.42</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9618</v>
       </c>
       <c r="J253" t="n">
-        <v>26.1414</v>
+        <v>25.9686</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.36</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8572</v>
+        <v>0.8398</v>
       </c>
       <c r="J254" t="n">
-        <v>23.1444</v>
+        <v>22.6746</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.05</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1563</v>
+        <v>0.1303</v>
       </c>
       <c r="J255" t="n">
-        <v>4.2201</v>
+        <v>3.5181</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.04</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1246</v>
+        <v>0.1009</v>
       </c>
       <c r="J256" t="n">
-        <v>3.3642</v>
+        <v>2.7243</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.12</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3288</v>
+        <v>0.2792</v>
       </c>
       <c r="J257" t="n">
-        <v>8.877599999999999</v>
+        <v>7.5384</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0256</v>
+        <v>0.02</v>
       </c>
       <c r="J258" t="n">
-        <v>0.6912</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1243</v>
+        <v>-0.1088</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.3561</v>
+        <v>-2.9376</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.78</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.258</v>
+        <v>-0.2391</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.966</v>
+        <v>-6.4557</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5451</v>
+        <v>-0.5513</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.7177</v>
+        <v>-14.8851</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.4</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7883</v>
+        <v>0.7433</v>
       </c>
       <c r="J262" t="n">
-        <v>18.9192</v>
+        <v>17.8392</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.87</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1717</v>
+        <v>-0.1527</v>
       </c>
       <c r="J263" t="n">
-        <v>-4.1208</v>
+        <v>-3.6648</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1717</v>
+        <v>-0.1527</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.1208</v>
+        <v>-3.6648</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.282</v>
+        <v>-0.2632</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.768</v>
+        <v>-6.3168</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.61</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4197</v>
+        <v>-0.4105</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.0728</v>
+        <v>-9.852</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.44</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0372</v>
+        <v>1.0409</v>
       </c>
       <c r="J267" t="n">
-        <v>24.8928</v>
+        <v>24.9816</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7088</v>
+        <v>0.6765</v>
       </c>
       <c r="J268" t="n">
-        <v>17.0112</v>
+        <v>16.236</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5572</v>
+        <v>0.5191</v>
       </c>
       <c r="J269" t="n">
-        <v>13.3728</v>
+        <v>12.4584</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.9</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3652</v>
+        <v>-0.3228</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.764799999999999</v>
+        <v>-7.7472</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.78</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6565</v>
+        <v>-0.6226</v>
       </c>
       <c r="J271" t="n">
-        <v>-15.756</v>
+        <v>-14.9424</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.17</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4022</v>
+        <v>0.3469</v>
       </c>
       <c r="J272" t="n">
-        <v>12.066</v>
+        <v>10.407</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3657</v>
+        <v>0.3118</v>
       </c>
       <c r="J273" t="n">
-        <v>10.971</v>
+        <v>9.353999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1134</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J274" t="n">
-        <v>3.402</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2742</v>
+        <v>-0.2551</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.226000000000001</v>
+        <v>-7.653</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.48</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5337</v>
+        <v>-0.5391</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.011</v>
+        <v>-16.173</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.53</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1563</v>
+        <v>1.1702</v>
       </c>
       <c r="J277" t="n">
-        <v>34.689</v>
+        <v>35.106</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.44</v>
       </c>
       <c r="I278" t="n">
-        <v>1.0279</v>
+        <v>1.0296</v>
       </c>
       <c r="J278" t="n">
-        <v>30.837</v>
+        <v>30.888</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.368</v>
+        <v>0.3322</v>
       </c>
       <c r="J279" t="n">
-        <v>11.04</v>
+        <v>9.965999999999999</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.02</v>
       </c>
       <c r="I280" t="n">
-        <v>0.0757</v>
+        <v>0.0592</v>
       </c>
       <c r="J280" t="n">
-        <v>2.271</v>
+        <v>1.776</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.9213</v>
+        <v>-0.9123</v>
       </c>
       <c r="J281" t="n">
-        <v>-27.639</v>
+        <v>-27.369</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.29</v>
       </c>
       <c r="I282" t="n">
-        <v>0.7876</v>
+        <v>0.7612</v>
       </c>
       <c r="J282" t="n">
-        <v>28.3536</v>
+        <v>27.4032</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.98</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0994</v>
+        <v>-0.0764</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.5784</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.93</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2595</v>
+        <v>-0.221</v>
       </c>
       <c r="J284" t="n">
-        <v>-9.342000000000001</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.91</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3151</v>
+        <v>-0.2741</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.3436</v>
+        <v>-9.867599999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.89</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3682</v>
+        <v>-0.3258</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.2552</v>
+        <v>-11.7288</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.85</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2399</v>
+        <v>1.2293</v>
       </c>
       <c r="J287" t="n">
-        <v>44.6364</v>
+        <v>44.2548</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2366</v>
+        <v>0.1957</v>
       </c>
       <c r="J288" t="n">
-        <v>8.5176</v>
+        <v>7.0452</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.08</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1974</v>
+        <v>0.1609</v>
       </c>
       <c r="J289" t="n">
-        <v>7.1064</v>
+        <v>5.7924</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.87</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1916</v>
+        <v>-0.1713</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.8976</v>
+        <v>-6.1668</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.77</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.293</v>
+        <v>-0.2758</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.548</v>
+        <v>-9.928800000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2599</v>
+        <v>1.2786</v>
       </c>
       <c r="J292" t="n">
-        <v>28.9777</v>
+        <v>29.4078</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2095</v>
+        <v>1.2267</v>
       </c>
       <c r="J293" t="n">
-        <v>27.8185</v>
+        <v>28.2141</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.54</v>
       </c>
       <c r="I294" t="n">
-        <v>1.1202</v>
+        <v>1.1358</v>
       </c>
       <c r="J294" t="n">
-        <v>25.7646</v>
+        <v>26.1234</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.37</v>
       </c>
       <c r="I295" t="n">
-        <v>0.859</v>
+        <v>0.8492</v>
       </c>
       <c r="J295" t="n">
-        <v>19.757</v>
+        <v>19.5316</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.97</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2079</v>
+        <v>-0.1814</v>
       </c>
       <c r="J296" t="n">
-        <v>-4.7817</v>
+        <v>-4.1722</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.96</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0412</v>
+        <v>-0.0292</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.9476</v>
+        <v>-0.6716</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1201</v>
+        <v>-0.105</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.7623</v>
+        <v>-2.415</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.86</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1661</v>
+        <v>-0.1505</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.8203</v>
+        <v>-3.4615</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.54</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4644</v>
+        <v>-0.4588</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.6812</v>
+        <v>-10.5524</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.46</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5341</v>
+        <v>-0.5373</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.2843</v>
+        <v>-12.3579</v>
       </c>
     </row>
   </sheetData>
